--- a/AAII_Financials/Quarterly/FDMT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FDMT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
   <si>
     <t>FDMT</t>
   </si>
@@ -656,164 +656,170 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43830</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43738</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43646</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43465</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43281</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E8" s="3">
         <v>20200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>13600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>14100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5100</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -874,8 +880,11 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -936,8 +945,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -960,70 +972,74 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>97100</v>
+      </c>
+      <c r="E12" s="3">
         <v>25100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>23600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>22400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>21500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>18900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>20400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>19400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>17500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>15800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>15200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>12800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>53000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>40400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>12400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>9400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>17000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>18400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>8200</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1084,8 +1100,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1113,8 +1132,8 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
@@ -1122,8 +1141,8 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1132,11 +1151,11 @@
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>5100</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1146,8 +1165,11 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1208,8 +1230,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1229,132 +1254,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>133600</v>
+      </c>
+      <c r="E17" s="3">
         <v>34200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>32400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>30400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>30000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>27000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>28600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>27600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>24900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>24000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>22200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>18300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>70300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>50800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>17600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>21900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>24500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10400</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-112900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-14000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-32200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-30100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-28800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-26500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-28400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-26400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-24800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-22600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-16300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-56700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-36200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-16300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-17100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-17500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-10400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-5300</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1377,132 +1409,139 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E20" s="3">
         <v>3700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2600</v>
-      </c>
-      <c r="F20" s="3">
-        <v>1400</v>
       </c>
       <c r="G20" s="3">
         <v>1400</v>
       </c>
       <c r="H20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I20" s="3">
         <v>800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>400</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-96600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-9300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-28500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-27700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-26400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-25200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-27600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-25900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-24700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-21900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-7200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-16000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-55300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-35100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-15800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-16400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-16100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-8900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-4800</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1563,70 +1602,76 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-100800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-10300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-29600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-28700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-27400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-25700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-28100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-26300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-25100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-22200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-7600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-16400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-56700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-36100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-16100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-16700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-16500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-9600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5200</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1687,8 +1732,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1749,132 +1797,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-100800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-10300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-29600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-28700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-27400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-25700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-28100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-26300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-25100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-22200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-16400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-56700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-36100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-16100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-16700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-16500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-9600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5200</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-100800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-10300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-29600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-28700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-27400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-25700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-28100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-26300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-25100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-22200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-16400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-56700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-36100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-16100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-16700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-16500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-9600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5200</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1935,8 +1992,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1997,8 +2057,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2059,8 +2122,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2121,132 +2187,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2600</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-1400</v>
       </c>
       <c r="G32" s="3">
         <v>-1400</v>
       </c>
       <c r="H32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="I32" s="3">
         <v>-800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-400</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-100800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-10300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-29600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-28700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-27400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-25700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-28100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-26300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-25100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-22200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-16400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-56700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-36100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-16100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-16700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-16500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-9600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5200</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2307,137 +2382,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-100800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-10300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-29600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-28700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-27400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-25700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-28100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-26300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-25100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-22200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-16400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-56700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-36100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-16100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-16700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-16500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-9600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5200</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43830</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43738</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43646</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43465</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43281</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2460,8 +2544,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2484,56 +2569,57 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>249100</v>
+      </c>
+      <c r="E41" s="3">
         <v>275700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>236300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>78600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>52400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>108300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>113500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>76000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>153000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>91000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>243700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>259900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>276700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>88800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>49700</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2546,41 +2632,44 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E42" s="3">
         <v>44000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>74000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>121900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>161200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>119400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>127600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>160200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>94800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>70700</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2596,8 +2685,8 @@
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -2608,19 +2697,22 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
+      <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3">
+        <v>0</v>
       </c>
       <c r="G43" s="3">
         <v>0</v>
@@ -2638,26 +2730,26 @@
         <v>0</v>
       </c>
       <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
         <v>800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1000</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2670,8 +2762,11 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2732,56 +2827,59 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E45" s="3">
         <v>8600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>4400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1900</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2794,56 +2892,59 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>296600</v>
+      </c>
+      <c r="E46" s="3">
         <v>328200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>317800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>207000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>220500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>232500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>246500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>243000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>256300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>165700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>248800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>264500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>282700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>92500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>52500</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2856,41 +2957,44 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="E47" s="3">
         <v>0</v>
       </c>
       <c r="F47" s="3">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3">
         <v>1400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>11100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>20500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>48400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>67700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>65500</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2906,8 +3010,8 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -2918,55 +3022,58 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>31700</v>
+      </c>
+      <c r="E48" s="3">
         <v>32700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>33600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>34300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>35300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>35500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>34900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>32600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>29000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>8800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5100</v>
-      </c>
-      <c r="P48" s="3">
-        <v>5000</v>
       </c>
       <c r="Q48" s="3">
         <v>5000</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
+      <c r="R48" s="3">
+        <v>5000</v>
       </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
@@ -2980,8 +3087,11 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3042,8 +3152,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3104,8 +3217,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3166,8 +3282,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3175,25 +3294,25 @@
         <v>700</v>
       </c>
       <c r="E52" s="3">
+        <v>700</v>
+      </c>
+      <c r="F52" s="3">
         <v>1100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1300</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1100</v>
       </c>
       <c r="H52" s="3">
         <v>1100</v>
       </c>
       <c r="I52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J52" s="3">
         <v>1000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>900</v>
-      </c>
-      <c r="K52" s="3">
-        <v>600</v>
       </c>
       <c r="L52" s="3">
         <v>600</v>
@@ -3208,13 +3327,13 @@
         <v>600</v>
       </c>
       <c r="P52" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="Q52" s="3">
         <v>700</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
+      <c r="R52" s="3">
+        <v>700</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
@@ -3228,8 +3347,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3290,56 +3412,59 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>339900</v>
+      </c>
+      <c r="E54" s="3">
         <v>361600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>352500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>244000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>261800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>280200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>302900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>324900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>353500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>240600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>254900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>270100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>288300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>98200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>58200</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3352,8 +3477,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3376,8 +3504,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3400,56 +3529,57 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E57" s="3">
         <v>4700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1700</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3462,8 +3592,11 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3524,56 +3657,59 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15400</v>
+      </c>
+      <c r="E59" s="3">
         <v>13500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>13000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11200</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3586,56 +3722,59 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E60" s="3">
         <v>18200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>13700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>15700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>14300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>16300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>13900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>16700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>13000</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3648,8 +3787,11 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3710,56 +3852,59 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E62" s="3">
         <v>13500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>14100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>14800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>15200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>16100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>16800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>18000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>13800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>15200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>13800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>15300</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3772,8 +3917,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3834,8 +3982,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3896,8 +4047,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3958,56 +4112,59 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E66" s="3">
         <v>31700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>27400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>25400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>30500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>28700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>30400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>28900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>34400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>27700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>31900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>28000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>28200</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4020,8 +4177,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4044,8 +4204,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4106,8 +4267,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4168,8 +4332,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4210,14 +4377,14 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>175400</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>103000</v>
       </c>
-      <c r="R70" s="3">
-        <v>0</v>
-      </c>
       <c r="S70" s="3">
         <v>0</v>
       </c>
@@ -4230,8 +4397,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4292,56 +4462,59 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-415300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-383000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-372800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-343200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-314500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-287100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-261400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-233300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-207000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-181900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-159700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-152100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-135700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-115100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-79000</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4354,8 +4527,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4416,8 +4592,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4478,8 +4657,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4540,56 +4722,59 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>307800</v>
+      </c>
+      <c r="E76" s="3">
         <v>329900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>325100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>218600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>231300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>251400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>272500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>296100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>319100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>224100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>240600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>242400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>256400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-105300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-73000</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4602,8 +4787,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4664,137 +4852,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43830</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43738</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43646</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43465</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43281</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-100800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-10300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-29600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-28700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-27400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-25700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-28100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-26300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-25100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-22200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-16400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-56700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-36100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-16100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-16700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-16500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-9600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5200</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4817,31 +5014,32 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E83" s="3">
         <v>1000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1100</v>
-      </c>
-      <c r="F83" s="3">
-        <v>1000</v>
       </c>
       <c r="G83" s="3">
         <v>1000</v>
       </c>
       <c r="H83" s="3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="I83" s="3">
         <v>500</v>
       </c>
       <c r="J83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="K83" s="3">
         <v>400</v>
@@ -4856,31 +5054,34 @@
         <v>400</v>
       </c>
       <c r="O83" s="3">
+        <v>400</v>
+      </c>
+      <c r="P83" s="3">
         <v>1400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1100</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>300</v>
       </c>
       <c r="R83" s="3">
         <v>300</v>
       </c>
       <c r="S83" s="3">
+        <v>300</v>
+      </c>
+      <c r="T83" s="3">
         <v>400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>300</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4941,8 +5142,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5003,8 +5207,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5065,8 +5272,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5127,8 +5337,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5189,70 +5402,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-75800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-22100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-27900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-22200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-21000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-19900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-23600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-21800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-15700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-16200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-15400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-50900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-33400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-8700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-10900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-17200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-16300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-6400</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5275,70 +5494,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1000</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-500</v>
       </c>
       <c r="Q91" s="3">
         <v>-500</v>
       </c>
       <c r="R91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="S91" s="3">
         <v>-1100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-400</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5399,8 +5622,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5461,70 +5687,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>115700</v>
+      </c>
+      <c r="E94" s="3">
         <v>30000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>49300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>43100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-35800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>15400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>57500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-54100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-32300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-139000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1000</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-500</v>
       </c>
       <c r="Q94" s="3">
         <v>-500</v>
       </c>
       <c r="R94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="S94" s="3">
         <v>-1100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-400</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5547,8 +5779,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5609,8 +5842,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5671,8 +5907,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5733,8 +5972,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5795,70 +6037,76 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>156800</v>
+      </c>
+      <c r="E100" s="3">
         <v>10600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>130500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>11000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>116100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>279000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>73000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>84600</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5919,66 +6167,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>196800</v>
+      </c>
+      <c r="E102" s="3">
         <v>39400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>157700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>26200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-55900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>37500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-77000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>62000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-152800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-16100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-16900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>227100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>39100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-9800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-13400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-18900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>67900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-6400</v>
       </c>
-      <c r="V102" s="3" t="s">
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FDMT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FDMT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="92">
   <si>
     <t>FDMT</t>
   </si>
@@ -656,170 +656,177 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43281</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
         <v>20700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>20200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>14600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>13600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>14600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>14100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5100</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -883,8 +890,11 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -948,8 +958,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -973,73 +986,77 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E12" s="3">
         <v>97100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>25100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>23600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>22400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>21500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>18900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>20400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>19400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>17500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>15800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>15200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>12800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>53000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>40400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>12400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>9400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>17000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>18400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>8200</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1103,8 +1120,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1135,8 +1155,8 @@
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
@@ -1144,8 +1164,8 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1154,11 +1174,11 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>5100</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1168,8 +1188,11 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1233,8 +1256,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1255,138 +1281,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>38200</v>
+      </c>
+      <c r="E17" s="3">
         <v>133600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>34200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>32400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>30400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>30000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>27000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>28600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>27600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>24900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>24000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>22200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>18300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>70300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>50800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>18300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>17600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>21900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>24500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10400</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3">
         <v>-112900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-14000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-32200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-30100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-28800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-26500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-28400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-26400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-24800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-22600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-16300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-56700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-36200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-16300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-17100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-17500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-10400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-5300</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1410,138 +1443,145 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
         <v>12100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2600</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1400</v>
       </c>
       <c r="H20" s="3">
         <v>1400</v>
       </c>
       <c r="I20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J20" s="3">
         <v>800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="3">
         <v>-96600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-9300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-28500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-27700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-26400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-25200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-27600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-25900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-24700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-21900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-7200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-16000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-55300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-35100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-15800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-16400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-16100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-8900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-4800</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1605,73 +1645,79 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-100800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-10300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-29600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-28700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-27400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-25700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-28100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-26300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-25100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-22200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-7600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-16400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-56700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-36100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-16100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-16700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-16500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-9600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-5200</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1735,8 +1781,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1800,138 +1849,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-100800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-10300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-29600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-28700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-27400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-25700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-28100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-26300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-25100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-22200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-16400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-56700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-36100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-16100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-16700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-16500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-9600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-5200</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-100800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-10300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-29600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-28700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-27400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-25700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-28100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-26300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-25100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-22200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-16400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-56700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-36100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-16100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-16700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-16500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-9600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-5200</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1995,8 +2053,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2060,8 +2121,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2125,8 +2189,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2190,138 +2257,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
         <v>-12100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2600</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-1400</v>
       </c>
       <c r="H32" s="3">
         <v>-1400</v>
       </c>
       <c r="I32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="J32" s="3">
         <v>-800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-100800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-10300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-29600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-28700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-27400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-25700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-28100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-26300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-25100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-22200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-16400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-56700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-36100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-16100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-16700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-16500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-9600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-5200</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2385,143 +2461,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-100800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-10300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-29600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-28700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-27400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-25700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-28100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-26300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-25100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-22200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-16400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-56700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-36100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-16100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-16700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-16500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-9600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-5200</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43281</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2545,8 +2630,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2570,59 +2656,60 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>275600</v>
+      </c>
+      <c r="E41" s="3">
         <v>249100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>275700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>236300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>78600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>52400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>108300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>113500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>76000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>153000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>91000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>243700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>259900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>276700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>88800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>49700</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2635,44 +2722,47 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>250300</v>
+      </c>
+      <c r="E42" s="3">
         <v>39100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>44000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>74000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>121900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>161200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>119400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>127600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>160200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>94800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>70700</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2688,8 +2778,8 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -2700,8 +2790,11 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2733,26 +2826,26 @@
         <v>0</v>
       </c>
       <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
         <v>800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1000</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2765,8 +2858,11 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2830,59 +2926,62 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E45" s="3">
         <v>8400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1900</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2895,59 +2994,62 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>535600</v>
+      </c>
+      <c r="E46" s="3">
         <v>296600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>328200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>317800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>207000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>220500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>232500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>246500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>243000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>256300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>165700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>248800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>264500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>282700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>92500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>52500</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2960,44 +3062,47 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>62900</v>
+      </c>
+      <c r="E47" s="3">
         <v>11000</v>
       </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
       <c r="F47" s="3">
         <v>0</v>
       </c>
       <c r="G47" s="3">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3">
         <v>1400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>11100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>20500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>48400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>67700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>65500</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3013,8 +3118,8 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U47" s="3">
         <v>0</v>
@@ -3025,58 +3130,61 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>30600</v>
+      </c>
+      <c r="E48" s="3">
         <v>31700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>32700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>33600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>34300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>35300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>35500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>34900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>32600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>29000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5100</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>5000</v>
       </c>
       <c r="R48" s="3">
         <v>5000</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
+      <c r="S48" s="3">
+        <v>5000</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
@@ -3090,8 +3198,11 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3155,8 +3266,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3220,8 +3334,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3285,37 +3402,40 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="E52" s="3">
         <v>700</v>
       </c>
       <c r="F52" s="3">
+        <v>700</v>
+      </c>
+      <c r="G52" s="3">
         <v>1100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1300</v>
-      </c>
-      <c r="H52" s="3">
-        <v>1100</v>
       </c>
       <c r="I52" s="3">
         <v>1100</v>
       </c>
       <c r="J52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K52" s="3">
         <v>1000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>900</v>
-      </c>
-      <c r="L52" s="3">
-        <v>600</v>
       </c>
       <c r="M52" s="3">
         <v>600</v>
@@ -3330,13 +3450,13 @@
         <v>600</v>
       </c>
       <c r="Q52" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="R52" s="3">
         <v>700</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
+      <c r="S52" s="3">
+        <v>700</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
@@ -3350,8 +3470,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3415,59 +3538,62 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>629900</v>
+      </c>
+      <c r="E54" s="3">
         <v>339900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>361600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>352500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>244000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>261800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>280200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>302900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>324900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>353500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>240600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>254900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>270100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>288300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>98200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>58200</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3480,8 +3606,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3505,8 +3634,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3530,59 +3660,60 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E57" s="3">
         <v>3500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1700</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3595,8 +3726,11 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3660,59 +3794,62 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E59" s="3">
         <v>15400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>13500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>12600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>15000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>13000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11200</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3725,59 +3862,62 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E60" s="3">
         <v>19000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>18200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>13700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>15700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>14300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>16300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>13900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>16700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>14300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>13000</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3790,8 +3930,11 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3855,59 +3998,62 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E62" s="3">
         <v>13100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>14100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>14800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>15200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>16100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>18000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>13800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>15200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>13800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>15300</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3920,8 +4066,11 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3985,8 +4134,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4050,8 +4202,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4115,59 +4270,62 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>29300</v>
+      </c>
+      <c r="E66" s="3">
         <v>32100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>31700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>27400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>25400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>30500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>28700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>30400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>28900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>34400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>16500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>27700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>31900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>28000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>28200</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4180,8 +4338,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4205,8 +4366,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4270,8 +4432,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4335,8 +4500,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4380,14 +4548,14 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>175400</v>
       </c>
-      <c r="R70" s="3">
+      <c r="S70" s="3">
         <v>103000</v>
       </c>
-      <c r="S70" s="3">
-        <v>0</v>
-      </c>
       <c r="T70" s="3">
         <v>0</v>
       </c>
@@ -4400,8 +4568,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4465,59 +4636,62 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-447700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-415300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-383000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-372800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-343200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-314500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-287100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-261400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-233300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-207000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-181900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-159700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-152100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-135700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-115100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-79000</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4530,8 +4704,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4595,8 +4772,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4660,8 +4840,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4725,59 +4908,62 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>600600</v>
+      </c>
+      <c r="E76" s="3">
         <v>307800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>329900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>325100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>218600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>231300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>251400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>272500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>296100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>319100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>224100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>240600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>242400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>256400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-105300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-73000</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,8 +4976,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4855,143 +5044,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43281</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-32400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-100800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-10300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-29600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-28700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-27400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-25700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-28100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-26300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-25100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-22200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-16400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-56700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-36100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-16100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-16700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-16500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-9600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-5200</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5015,34 +5213,35 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E83" s="3">
         <v>4200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>1000</v>
       </c>
       <c r="H83" s="3">
         <v>1000</v>
       </c>
       <c r="I83" s="3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="J83" s="3">
         <v>500</v>
       </c>
       <c r="K83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="L83" s="3">
         <v>400</v>
@@ -5057,31 +5256,34 @@
         <v>400</v>
       </c>
       <c r="P83" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q83" s="3">
         <v>1400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1100</v>
-      </c>
-      <c r="R83" s="3">
-        <v>300</v>
       </c>
       <c r="S83" s="3">
         <v>300</v>
       </c>
       <c r="T83" s="3">
+        <v>300</v>
+      </c>
+      <c r="U83" s="3">
         <v>400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>300</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5145,8 +5347,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5210,8 +5415,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5275,8 +5483,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5340,8 +5551,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5405,73 +5619,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-29100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-75800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-22100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-27900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-22200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-21000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-19900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-23600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-21800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-15700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-16200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-15400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-50900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-33400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-8700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-10900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-17200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-16300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-6400</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5495,73 +5715,77 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1000</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-500</v>
       </c>
       <c r="R91" s="3">
         <v>-500</v>
       </c>
       <c r="S91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="T91" s="3">
         <v>-1100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-400</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5625,8 +5849,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5690,73 +5917,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-263300</v>
+      </c>
+      <c r="E94" s="3">
         <v>115700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>30000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>49300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>43100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-35800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>15400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>57500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-54100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-32300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-139000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1000</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-500</v>
       </c>
       <c r="R94" s="3">
         <v>-500</v>
       </c>
       <c r="S94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="T94" s="3">
         <v>-1100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-400</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5780,8 +6013,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5845,8 +6079,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5910,8 +6147,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5975,8 +6215,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6040,73 +6283,79 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>318800</v>
+      </c>
+      <c r="E100" s="3">
         <v>156800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>10600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>130500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>11000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>116100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>279000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>73000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>84600</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6170,69 +6419,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E102" s="3">
         <v>196800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>39400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>157700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>26200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-55900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>37500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-77000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>62000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-152800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-16100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-16900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>227100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>39100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-9800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-13400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-18900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>67900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-6400</v>
       </c>
-      <c r="W102" s="3" t="s">
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FDMT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FDMT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
   <si>
     <t>FDMT</t>
   </si>
@@ -656,109 +656,113 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -766,67 +770,70 @@
         <v>3</v>
       </c>
       <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
         <v>20700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>20200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>14600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>13600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>14600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>14100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5100</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -893,8 +900,11 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -961,8 +971,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -987,76 +1000,80 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E12" s="3">
         <v>27900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>97100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>25100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>23600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>22400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>21500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>18900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>20400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>19400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>17500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>15800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>15200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>12800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>53000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>40400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>12400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>9400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>17000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>18400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>8200</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1123,8 +1140,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1158,8 +1178,8 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
@@ -1167,8 +1187,8 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1177,11 +1197,11 @@
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>5100</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1191,8 +1211,11 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1259,8 +1282,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1282,76 +1308,80 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E17" s="3">
         <v>38200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>133600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>34200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>32400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>30400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>30000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>27000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>28600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>27600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>24900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>24000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>22200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>18300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>70300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>50800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>18300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>17600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>21900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>24500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10400</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1359,67 +1389,70 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-38200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-112900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-14000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-32200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-30100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-28800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-26500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-28400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-26400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-24800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-22600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-7600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-16300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-56700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-36200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-16300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-17100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-17500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-10400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5300</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1444,8 +1477,9 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1453,67 +1487,70 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F20" s="3">
         <v>12100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2600</v>
-      </c>
-      <c r="H20" s="3">
-        <v>1400</v>
       </c>
       <c r="I20" s="3">
         <v>1400</v>
       </c>
       <c r="J20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K20" s="3">
         <v>800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>400</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1521,67 +1558,70 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-31200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-96600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-9300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-28500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-27700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-26400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-25200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-27600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-25900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-24700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-21900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-7200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-55300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-35100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-15800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-16400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-16100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-8900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-4800</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1648,76 +1688,82 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-32400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-100800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-29600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-28700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-27400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-25700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-28100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-26300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-25100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-22200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-7600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-56700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-36100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-16100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-16700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-16500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-9600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5200</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1784,8 +1830,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1852,144 +1901,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-32400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-100800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-29600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-28700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-27400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-25700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-28100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-26300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-25100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-22200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-56700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-36100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-16100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-16700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-16500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-9600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-5200</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-32400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-100800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-29600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-28700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-27400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-25700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-28100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-26300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-25100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-22200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-56700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-36100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-16100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-16700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-16500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-9600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-5200</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2056,8 +2114,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2124,8 +2185,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2192,8 +2256,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2260,8 +2327,11 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2269,135 +2339,141 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="F32" s="3">
         <v>-12100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2600</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-1400</v>
       </c>
       <c r="I32" s="3">
         <v>-1400</v>
       </c>
       <c r="J32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-400</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-32400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-100800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-29600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-28700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-27400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-25700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-28100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-26300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-25100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-22200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-56700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-36100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-16100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-16700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-16500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-9600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-5200</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2464,149 +2540,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-32400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-100800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-29600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-28700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-27400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-25700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-28100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-26300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-25100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-22200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-56700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-36100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-16100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-16700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-16500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-9600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-5200</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2631,8 +2716,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2657,62 +2743,63 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>189100</v>
+      </c>
+      <c r="E41" s="3">
         <v>275600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>249100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>275700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>236300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>78600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>52400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>108300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>113500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>76000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>153000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>91000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>243700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>259900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>276700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>88800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>49700</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2725,47 +2812,50 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>352900</v>
+      </c>
+      <c r="E42" s="3">
         <v>250300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>39100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>44000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>74000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>121900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>161200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>119400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>127600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>160200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>94800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>70700</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2781,8 +2871,8 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -2793,8 +2883,11 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2829,26 +2922,26 @@
         <v>0</v>
       </c>
       <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
         <v>800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1000</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2861,8 +2954,11 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2929,62 +3025,65 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E45" s="3">
         <v>9700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>4800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>8500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>4400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1900</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2997,62 +3096,65 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>552600</v>
+      </c>
+      <c r="E46" s="3">
         <v>535600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>296600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>328200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>317800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>207000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>220500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>232500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>246500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>243000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>256300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>165700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>248800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>264500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>282700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>92500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>52500</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3065,47 +3167,50 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>35700</v>
+      </c>
+      <c r="E47" s="3">
         <v>62900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>11000</v>
       </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
       <c r="G47" s="3">
         <v>0</v>
       </c>
       <c r="H47" s="3">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3">
         <v>1400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>11100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>20500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>48400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>67700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>65500</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3121,8 +3226,8 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="U47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -3133,61 +3238,64 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E48" s="3">
         <v>30600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>31700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>32700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>33600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>34300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>35300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>35500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>34900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>32600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>29000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5100</v>
-      </c>
-      <c r="R48" s="3">
-        <v>5000</v>
       </c>
       <c r="S48" s="3">
         <v>5000</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
+      <c r="T48" s="3">
+        <v>5000</v>
       </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
@@ -3201,8 +3309,11 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3269,8 +3380,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3337,8 +3451,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3405,40 +3522,43 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E52" s="3">
         <v>800</v>
-      </c>
-      <c r="E52" s="3">
-        <v>700</v>
       </c>
       <c r="F52" s="3">
         <v>700</v>
       </c>
       <c r="G52" s="3">
+        <v>700</v>
+      </c>
+      <c r="H52" s="3">
         <v>1100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1300</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1100</v>
       </c>
       <c r="J52" s="3">
         <v>1100</v>
       </c>
       <c r="K52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="L52" s="3">
         <v>1000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>900</v>
-      </c>
-      <c r="M52" s="3">
-        <v>600</v>
       </c>
       <c r="N52" s="3">
         <v>600</v>
@@ -3453,13 +3573,13 @@
         <v>600</v>
       </c>
       <c r="R52" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="S52" s="3">
         <v>700</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
+      <c r="T52" s="3">
+        <v>700</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
@@ -3473,8 +3593,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3541,62 +3664,65 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>620100</v>
+      </c>
+      <c r="E54" s="3">
         <v>629900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>339900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>361600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>352500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>244000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>261800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>280200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>302900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>324900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>353500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>240600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>254900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>270100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>288300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>98200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>58200</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3609,8 +3735,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3635,8 +3764,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3661,62 +3791,63 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E57" s="3">
         <v>4200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1700</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3729,8 +3860,11 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3797,62 +3931,65 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>16000</v>
+      </c>
+      <c r="E59" s="3">
         <v>12200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>15400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>13500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>13000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11200</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3865,62 +4002,65 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19400</v>
+      </c>
+      <c r="E60" s="3">
         <v>16400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>18200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>13700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>15700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>13600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>14300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>16300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>13900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>16700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>14300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>13000</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3933,8 +4073,11 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4001,62 +4144,65 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E62" s="3">
         <v>12900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>13100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>13500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>13600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>14100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>14800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>15200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>18000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>13800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>15200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>13800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>15300</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4069,8 +4215,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4137,8 +4286,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4205,8 +4357,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4273,62 +4428,65 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E66" s="3">
         <v>29300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>32100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>31700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>27400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>25400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>30500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>28700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>30400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>28900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>34400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>27700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>31900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>28000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>28200</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4341,8 +4499,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4367,8 +4528,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4435,8 +4597,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4503,8 +4668,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4551,14 +4719,14 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>175400</v>
       </c>
-      <c r="S70" s="3">
+      <c r="T70" s="3">
         <v>103000</v>
       </c>
-      <c r="T70" s="3">
-        <v>0</v>
-      </c>
       <c r="U70" s="3">
         <v>0</v>
       </c>
@@ -4571,8 +4739,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4639,62 +4810,65 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-482700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-447700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-415300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-383000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-372800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-343200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-314500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-287100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-261400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-233300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-207000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-181900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-159700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-152100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-135700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-115100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-79000</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4707,8 +4881,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4775,8 +4952,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4843,8 +5023,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4911,62 +5094,65 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>588300</v>
+      </c>
+      <c r="E76" s="3">
         <v>600600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>307800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>329900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>325100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>218600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>231300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>251400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>272500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>296100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>319100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>224100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>240600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>242400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>256400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-105300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-73000</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4979,8 +5165,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5047,149 +5236,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-32400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-100800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-29600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-28700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-27400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-25700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-28100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-26300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-25100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-22200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-56700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-36100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-16100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-16700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-16500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-9600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-5200</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5214,8 +5412,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5223,28 +5422,28 @@
         <v>1200</v>
       </c>
       <c r="E83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F83" s="3">
         <v>4200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>1000</v>
       </c>
       <c r="I83" s="3">
         <v>1000</v>
       </c>
       <c r="J83" s="3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="K83" s="3">
         <v>500</v>
       </c>
       <c r="L83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="M83" s="3">
         <v>400</v>
@@ -5259,31 +5458,34 @@
         <v>400</v>
       </c>
       <c r="Q83" s="3">
+        <v>400</v>
+      </c>
+      <c r="R83" s="3">
         <v>1400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1100</v>
-      </c>
-      <c r="S83" s="3">
-        <v>300</v>
       </c>
       <c r="T83" s="3">
         <v>300</v>
       </c>
       <c r="U83" s="3">
+        <v>300</v>
+      </c>
+      <c r="V83" s="3">
         <v>400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>300</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5350,8 +5552,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5418,8 +5623,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5486,8 +5694,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5554,8 +5765,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5622,76 +5836,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-30200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-29100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-75800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-22100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-27900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-22200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-21000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-19900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-23600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-21800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-15700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-16200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-15400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-50900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-33400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-8700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-10900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-17200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-16300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-6400</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5716,76 +5936,80 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1000</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-500</v>
       </c>
       <c r="S91" s="3">
         <v>-500</v>
       </c>
       <c r="T91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="U91" s="3">
         <v>-1100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-400</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5852,8 +6076,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5920,76 +6147,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-73500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-263300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>115700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>30000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>49300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>43100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-35800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>15400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>57500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-54100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-32300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-139000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1000</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-500</v>
       </c>
       <c r="S94" s="3">
         <v>-500</v>
       </c>
       <c r="T94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="U94" s="3">
         <v>-1100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-400</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6014,8 +6247,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6082,8 +6316,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6150,8 +6387,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6218,8 +6458,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6286,76 +6529,82 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E100" s="3">
         <v>318800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>156800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>10600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>130500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>11000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>116100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>279000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>73000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>84600</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6422,72 +6671,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-86500</v>
+      </c>
+      <c r="E102" s="3">
         <v>26500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>196800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>39400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>157700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>26200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-55900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>37500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-77000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>62000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-152800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-16100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-16900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>227100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>39100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-9800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-13400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-18900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>67900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-6400</v>
       </c>
-      <c r="X102" s="3" t="s">
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FDMT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FDMT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
   <si>
     <t>FDMT</t>
   </si>
@@ -656,113 +656,117 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -773,90 +777,93 @@
         <v>0</v>
       </c>
       <c r="F8" s="3">
-        <v>20700</v>
-      </c>
-      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3">
         <v>20200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>13600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>14600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>14100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5100</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>31900</v>
+      </c>
+      <c r="F9" s="3">
+        <v>27900</v>
+      </c>
+      <c r="G9" s="3">
+        <v>26000</v>
+      </c>
+      <c r="H9" s="3">
+        <v>25100</v>
+      </c>
+      <c r="I9" s="3">
+        <v>23600</v>
+      </c>
+      <c r="J9" s="3">
+        <v>22400</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -903,31 +910,34 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>-38500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-31900</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="G10" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="H10" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="J10" s="3">
+        <v>-22100</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -974,8 +984,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1001,79 +1014,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E12" s="3">
         <v>31900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>27900</v>
       </c>
-      <c r="F12" s="3">
-        <v>97100</v>
-      </c>
       <c r="G12" s="3">
+        <v>26000</v>
+      </c>
+      <c r="H12" s="3">
         <v>25100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>23600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>22400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>21500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>18900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>20400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>19400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>17500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>15800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>15200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>12800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>53000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>40400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>12400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>9400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>17000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>18400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>8200</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1143,31 +1160,34 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1181,8 +1201,8 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
@@ -1190,8 +1210,8 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1200,11 +1220,11 @@
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>5100</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1214,31 +1234,34 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1285,8 +1308,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1309,150 +1335,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>51100</v>
+      </c>
+      <c r="E17" s="3">
         <v>42500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>38200</v>
       </c>
-      <c r="F17" s="3">
-        <v>133600</v>
-      </c>
       <c r="G17" s="3">
+        <v>36600</v>
+      </c>
+      <c r="H17" s="3">
         <v>34200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>32400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>30400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>30000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>27000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>28600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>27600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>24900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>24000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>22200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>18300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>70300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>50800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>18300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>17600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>21900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>24500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10400</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-51100</v>
       </c>
       <c r="E18" s="3">
-        <v>-38200</v>
+        <v>-42500</v>
       </c>
       <c r="F18" s="3">
-        <v>-112900</v>
+        <v>-38100</v>
       </c>
       <c r="G18" s="3">
+        <v>-36700</v>
+      </c>
+      <c r="H18" s="3">
         <v>-14000</v>
       </c>
-      <c r="H18" s="3">
-        <v>-32200</v>
-      </c>
       <c r="I18" s="3">
+        <v>-32100</v>
+      </c>
+      <c r="J18" s="3">
         <v>-30100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-28800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-26500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-28400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-26400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-24800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-22600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-16300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-56700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-36200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-16300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-17100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-17500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-10400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1478,173 +1511,180 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>5800</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>12100</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>3700</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>2600</v>
+        <v>200</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>1400</v>
       </c>
-      <c r="J20" s="3">
-        <v>1400</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>400</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-49900</v>
       </c>
       <c r="E21" s="3">
-        <v>-31200</v>
+        <v>-41300</v>
       </c>
       <c r="F21" s="3">
-        <v>-96600</v>
+        <v>-37000</v>
       </c>
       <c r="G21" s="3">
-        <v>-9300</v>
+        <v>-35600</v>
       </c>
       <c r="H21" s="3">
-        <v>-28500</v>
+        <v>-13100</v>
       </c>
       <c r="I21" s="3">
-        <v>-27700</v>
+        <v>-31000</v>
       </c>
       <c r="J21" s="3">
+        <v>-29100</v>
+      </c>
+      <c r="K21" s="3">
         <v>-26400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-25200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-27600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-25900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-24700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-21900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-16000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-55300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-35100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-15800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-16400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-16100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-8900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1691,102 +1731,108 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-43800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-35000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-32400</v>
       </c>
-      <c r="F23" s="3">
-        <v>-100800</v>
-      </c>
       <c r="G23" s="3">
+        <v>-32300</v>
+      </c>
+      <c r="H23" s="3">
         <v>-10300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-29600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-28700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-27400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-25700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-28100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-26300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-25100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-22200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-16400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-56700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-36100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-16100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-16700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-16500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-9600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1833,8 +1879,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1904,150 +1953,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-43800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-35000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-32400</v>
       </c>
-      <c r="F26" s="3">
-        <v>-100800</v>
-      </c>
       <c r="G26" s="3">
+        <v>-32300</v>
+      </c>
+      <c r="H26" s="3">
         <v>-10300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-29600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-28700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-27400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-25700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-28100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-26300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-25100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-22200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-16400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-56700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-36100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-16100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-16700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-16500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-9600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-43800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-35000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-32400</v>
       </c>
-      <c r="F27" s="3">
-        <v>-100800</v>
-      </c>
       <c r="G27" s="3">
+        <v>-32300</v>
+      </c>
+      <c r="H27" s="3">
         <v>-10300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-29600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-28700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-27400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-25700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-28100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-26300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-25100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-22200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-16400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-56700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-36100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-16100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-16700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-16500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-9600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2117,8 +2175,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2188,8 +2249,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2259,8 +2323,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2330,150 +2397,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-5800</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-12100</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-3700</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>-2600</v>
+        <v>-200</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1400</v>
       </c>
-      <c r="J32" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-400</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-43800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-35000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-32400</v>
       </c>
-      <c r="F33" s="3">
-        <v>-100800</v>
-      </c>
       <c r="G33" s="3">
+        <v>-32300</v>
+      </c>
+      <c r="H33" s="3">
         <v>-10300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-29600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-28700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-27400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-25700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-28100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-26300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-25100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-22200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-16400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-56700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-36100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-16100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-16700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-16500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-9600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2543,155 +2619,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-43800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-35000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-32400</v>
       </c>
-      <c r="F35" s="3">
-        <v>-100800</v>
-      </c>
       <c r="G35" s="3">
+        <v>-32300</v>
+      </c>
+      <c r="H35" s="3">
         <v>-10300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-29600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-28700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-27400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-25700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-28100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-26300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-25100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-22200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-16400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-56700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-36100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-16100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-16700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-16500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-9600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2717,8 +2802,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2744,65 +2830,66 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>187500</v>
+      </c>
+      <c r="E41" s="3">
         <v>189100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>275600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>249100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>275700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>236300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>78600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>52400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>108300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>113500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>76000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>153000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>91000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>243700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>259900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>276700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>88800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>49700</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2815,50 +2902,53 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>314400</v>
+      </c>
+      <c r="E42" s="3">
         <v>352900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>250300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>39100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>44000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>74000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>121900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>161200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>119400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>127600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>160200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>94800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>70700</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2874,8 +2964,8 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -2886,31 +2976,34 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2925,26 +3018,26 @@
         <v>0</v>
       </c>
       <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3">
         <v>800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1000</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2957,31 +3050,34 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3028,65 +3124,68 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>10700</v>
-      </c>
-      <c r="E45" s="3">
-        <v>9700</v>
-      </c>
-      <c r="F45" s="3">
-        <v>8400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>8600</v>
-      </c>
-      <c r="H45" s="3">
-        <v>7400</v>
-      </c>
-      <c r="I45" s="3">
-        <v>6600</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>7000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>4800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1900</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3099,65 +3198,68 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>510800</v>
+      </c>
+      <c r="E46" s="3">
         <v>552600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>535600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>296600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>328200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>317800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>207000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>220500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>232500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>246500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>243000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>256300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>165700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>248800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>264500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>282700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>92500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>52500</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3170,50 +3272,53 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>48800</v>
+      </c>
+      <c r="E47" s="3">
         <v>35700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>62900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>11000</v>
       </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3">
         <v>1400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>11100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>20500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>48400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>67700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>65500</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3229,8 +3334,8 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -3241,64 +3346,67 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E48" s="3">
         <v>29400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>30600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>31700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>32700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>33600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>34300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>35300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>35500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>34900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>32600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>29000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5100</v>
-      </c>
-      <c r="S48" s="3">
-        <v>5000</v>
       </c>
       <c r="T48" s="3">
         <v>5000</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
+      <c r="U48" s="3">
+        <v>5000</v>
       </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
@@ -3312,8 +3420,11 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3383,8 +3494,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3454,8 +3568,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3525,43 +3642,46 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E52" s="3">
         <v>2300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>800</v>
-      </c>
-      <c r="F52" s="3">
-        <v>700</v>
       </c>
       <c r="G52" s="3">
         <v>700</v>
       </c>
       <c r="H52" s="3">
+        <v>700</v>
+      </c>
+      <c r="I52" s="3">
         <v>1100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1300</v>
-      </c>
-      <c r="J52" s="3">
-        <v>1100</v>
       </c>
       <c r="K52" s="3">
         <v>1100</v>
       </c>
       <c r="L52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M52" s="3">
         <v>1000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>900</v>
-      </c>
-      <c r="N52" s="3">
-        <v>600</v>
       </c>
       <c r="O52" s="3">
         <v>600</v>
@@ -3576,13 +3696,13 @@
         <v>600</v>
       </c>
       <c r="S52" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="T52" s="3">
         <v>700</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
+      <c r="U52" s="3">
+        <v>700</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
@@ -3596,8 +3716,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3667,65 +3790,68 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>604000</v>
+      </c>
+      <c r="E54" s="3">
         <v>620100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>629900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>339900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>361600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>352500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>244000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>261800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>280200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>302900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>324900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>353500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>240600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>254900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>270100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>288300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>98200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>58200</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3738,8 +3864,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3765,8 +3894,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3792,65 +3922,66 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E57" s="3">
         <v>3400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1700</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3863,31 +3994,34 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>3100</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3934,65 +4068,68 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>16000</v>
-      </c>
-      <c r="E59" s="3">
-        <v>12200</v>
-      </c>
-      <c r="F59" s="3">
-        <v>15400</v>
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G59" s="3">
-        <v>13500</v>
+        <v>300</v>
       </c>
       <c r="H59" s="3">
-        <v>10300</v>
+        <v>100</v>
       </c>
       <c r="I59" s="3">
-        <v>8900</v>
+        <v>600</v>
       </c>
       <c r="J59" s="3">
+        <v>800</v>
+      </c>
+      <c r="K59" s="3">
         <v>12400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>12600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>15000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>13000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11200</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4005,65 +4142,68 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>29500</v>
+      </c>
+      <c r="E60" s="3">
         <v>19400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>16400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>19000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>18200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>13700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>15700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>14300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>12100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>16300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>13900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>16700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>14300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>13000</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4076,31 +4216,34 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>19700</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>10500</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>11500</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>12500</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>13000</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4147,65 +4290,68 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>12400</v>
+        <v>600</v>
       </c>
       <c r="E62" s="3">
-        <v>12900</v>
+        <v>600</v>
       </c>
       <c r="F62" s="3">
-        <v>13100</v>
+        <v>600</v>
       </c>
       <c r="G62" s="3">
-        <v>13500</v>
+        <v>600</v>
       </c>
       <c r="H62" s="3">
-        <v>13600</v>
+        <v>400</v>
       </c>
       <c r="I62" s="3">
-        <v>14100</v>
+        <v>200</v>
       </c>
       <c r="J62" s="3">
+        <v>200</v>
+      </c>
+      <c r="K62" s="3">
         <v>14800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>15200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>16100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>16800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>18000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>13800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>15200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>13800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>15300</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4218,8 +4364,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4289,8 +4438,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4360,8 +4512,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4431,65 +4586,68 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>51100</v>
+      </c>
+      <c r="E66" s="3">
         <v>31800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>29300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>32100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>31700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>27400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>25400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>30500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>28700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>30400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>28900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>34400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>27700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>31900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>28000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>28200</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4502,8 +4660,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4529,8 +4690,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4600,8 +4762,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4671,8 +4836,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4722,14 +4890,14 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>175400</v>
       </c>
-      <c r="T70" s="3">
+      <c r="U70" s="3">
         <v>103000</v>
       </c>
-      <c r="U70" s="3">
-        <v>0</v>
-      </c>
       <c r="V70" s="3">
         <v>0</v>
       </c>
@@ -4742,8 +4910,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4813,65 +4984,68 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-526500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-482700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-447700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-415300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-383000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-372800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-343200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-314500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-287100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-261400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-233300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-207000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-181900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-159700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-152100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-135700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-115100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-79000</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4884,8 +5058,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4955,8 +5132,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5026,8 +5206,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5097,65 +5280,68 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>552900</v>
+      </c>
+      <c r="E76" s="3">
         <v>588300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>600600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>307800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>329900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>325100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>218600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>231300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>251400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>272500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>296100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>319100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>224100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>240600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>242400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>256400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-105300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-73000</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5168,8 +5354,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5239,155 +5428,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-43800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-35000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-32400</v>
       </c>
-      <c r="F81" s="3">
-        <v>-100800</v>
-      </c>
       <c r="G81" s="3">
+        <v>-32300</v>
+      </c>
+      <c r="H81" s="3">
         <v>-10300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-29600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-28700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-27400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-25700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-28100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-26300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-25100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-22200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-16400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-56700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-36100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-16100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-16700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-16500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-9600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5413,40 +5611,41 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="E83" s="3">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="F83" s="3">
-        <v>4200</v>
+        <v>1400</v>
       </c>
       <c r="G83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H83" s="3">
+        <v>900</v>
+      </c>
+      <c r="I83" s="3">
+        <v>800</v>
+      </c>
+      <c r="J83" s="3">
+        <v>800</v>
+      </c>
+      <c r="K83" s="3">
         <v>1000</v>
-      </c>
-      <c r="H83" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I83" s="3">
-        <v>1000</v>
-      </c>
-      <c r="J83" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>500</v>
       </c>
       <c r="L83" s="3">
         <v>500</v>
       </c>
       <c r="M83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="N83" s="3">
         <v>400</v>
@@ -5461,31 +5660,34 @@
         <v>400</v>
       </c>
       <c r="R83" s="3">
+        <v>400</v>
+      </c>
+      <c r="S83" s="3">
         <v>1400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1100</v>
-      </c>
-      <c r="T83" s="3">
-        <v>300</v>
       </c>
       <c r="U83" s="3">
         <v>300</v>
       </c>
       <c r="V83" s="3">
+        <v>300</v>
+      </c>
+      <c r="W83" s="3">
         <v>400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>300</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5555,8 +5757,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5626,8 +5831,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5697,8 +5905,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5768,8 +5979,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5839,79 +6053,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-29400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-30200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-29100</v>
       </c>
-      <c r="F89" s="3">
-        <v>-75800</v>
-      </c>
       <c r="G89" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="H89" s="3">
         <v>-1200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-22100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-27900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-22200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-21000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-19900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-23600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-21800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-15700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-16200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-15400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-50900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-33400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-8700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-10900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-17200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-16300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-6400</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5937,79 +6157,83 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1000</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-500</v>
       </c>
       <c r="T91" s="3">
         <v>-500</v>
       </c>
       <c r="U91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="V91" s="3">
         <v>-1100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-400</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6079,8 +6303,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6150,79 +6377,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-73500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-263300</v>
       </c>
-      <c r="F94" s="3">
-        <v>115700</v>
-      </c>
       <c r="G94" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="H94" s="3">
         <v>30000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>49300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>43100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-35800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>15400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>57500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-54100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-32300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-139000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1000</v>
-      </c>
-      <c r="S94" s="3">
-        <v>-500</v>
       </c>
       <c r="T94" s="3">
         <v>-500</v>
       </c>
       <c r="U94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="V94" s="3">
         <v>-1100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-400</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6248,31 +6481,32 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6319,8 +6553,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6390,8 +6627,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6461,8 +6701,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6532,102 +6775,108 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>600</v>
+      </c>
+      <c r="E100" s="3">
         <v>17200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>318800</v>
       </c>
-      <c r="F100" s="3">
-        <v>156800</v>
-      </c>
       <c r="G100" s="3">
+        <v>4800</v>
+      </c>
+      <c r="H100" s="3">
         <v>10600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>130500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>11000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>116100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>279000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>73000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>84600</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6674,75 +6923,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-86500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>26500</v>
       </c>
-      <c r="F102" s="3">
-        <v>196800</v>
-      </c>
       <c r="G102" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="H102" s="3">
         <v>39400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>157700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>26200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-55900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>37500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-77000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>62000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-152800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-16900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>227100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>39100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-9800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-13400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-18900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>67900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-6400</v>
       </c>
-      <c r="Y102" s="3" t="s">
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FDMT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FDMT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
   <si>
     <t>FDMT</t>
   </si>
@@ -656,117 +656,120 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -779,95 +782,98 @@
       <c r="F8" s="3">
         <v>0</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3">
         <v>20200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>14600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>13600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>14600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>14100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5100</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>43100</v>
+      </c>
+      <c r="E9" s="3">
         <v>38500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>31900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>27900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>26000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>25100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>23600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>22400</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -913,35 +919,38 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-43100</v>
+      </c>
+      <c r="E10" s="3">
         <v>-38500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-31900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-27800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-26000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-4900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-23300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-22100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -987,8 +996,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1015,82 +1027,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>43100</v>
+      </c>
+      <c r="E12" s="3">
         <v>38500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>31900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>27900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>26000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>25100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>23600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>22400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>21500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>18900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>20400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>19400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>17500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>15800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>15200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>12800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>53000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>40400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>12400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>9400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>17000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>18400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>8200</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1163,8 +1179,11 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1189,8 +1208,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1204,8 +1223,8 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
@@ -1213,8 +1232,8 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1223,11 +1242,11 @@
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>5100</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1237,13 +1256,16 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="E15" s="3">
         <v>1200</v>
@@ -1252,20 +1274,20 @@
         <v>1200</v>
       </c>
       <c r="G15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H15" s="3">
         <v>1100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1311,8 +1333,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,156 +1361,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>56100</v>
+      </c>
+      <c r="E17" s="3">
         <v>51100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>42500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>38200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>36600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>34200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>32400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>30400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>30000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>27000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>28600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>27600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>24900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>24000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>22200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>18300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>70300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>50800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>18300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>17600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>21900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>24500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>10400</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-56100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-51100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-42500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-38100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-36700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-14000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-32100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-30100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-28800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-26500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-28400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-26400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-24800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-22600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-7600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-16300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-56700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-36200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-16300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-17100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-17500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-10400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,8 +1544,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1530,138 +1563,144 @@
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>1400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>400</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-55000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-49900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-41300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-37000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-35600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-13100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-31000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-29100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-26400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-25200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-27600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-25900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-24700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-21900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-7200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-16000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-55300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-35100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-15800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-16400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-16100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-8900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1686,8 +1725,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1734,82 +1773,88 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-49700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-43800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-35000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-32400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-32300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-10300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-29600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-28700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-27400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-25700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-28100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-26300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-25100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-22200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-7600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-16400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-56700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-36100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-16100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-16700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-16500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-9600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1834,8 +1879,8 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1882,8 +1927,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,156 +2004,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-49700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-43800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-35000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-32400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-32300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-10300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-29600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-28700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-27400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-25700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-28100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-26300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-25100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-22200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-7600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-16400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-56700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-36100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-16100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-16700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-16500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-9600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-49700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-43800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-35000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-32400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-32300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-10300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-29600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-28700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-27400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-25700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-28100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-26300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-25100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-22200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-16400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-56700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-36100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-16100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-16700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-16500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-9600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2235,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2252,8 +2312,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2389,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,8 +2466,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2418,138 +2487,144 @@
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-1400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-400</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-49700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-43800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-35000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-32400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-32300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-10300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-29600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-28700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-27400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-25700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-28100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-26300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-25100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-22200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-16400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-56700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-36100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-16100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-16700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-16500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-9600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,161 +2697,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-49700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-43800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-35000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-32400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-32300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-10300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-29600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-28700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-27400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-25700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-28100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-26300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-25100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-22200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-16400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-56700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-36100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-16100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-16700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-16500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-9600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2887,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,68 +2916,69 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>149300</v>
+      </c>
+      <c r="E41" s="3">
         <v>187500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>189100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>275600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>249100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>275700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>236300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>78600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>52400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>108300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>113500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>76000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>153000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>91000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>243700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>259900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>276700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>88800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>49700</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2905,53 +2991,56 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>275500</v>
+      </c>
+      <c r="E42" s="3">
         <v>314400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>352900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>250300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>39100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>44000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>74000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>121900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>161200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>119400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>127600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>160200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>94800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>70700</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2967,8 +3056,8 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
@@ -2979,8 +3068,11 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3005,8 +3097,8 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -3021,26 +3113,26 @@
         <v>0</v>
       </c>
       <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
         <v>800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1000</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3053,8 +3145,11 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3079,8 +3174,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3127,8 +3222,11 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3153,42 +3251,42 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>7000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>4800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1900</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3201,68 +3299,71 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>434900</v>
+      </c>
+      <c r="E46" s="3">
         <v>510800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>552600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>535600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>296600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>328200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>317800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>207000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>220500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>232500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>246500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>243000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>256300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>165700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>248800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>264500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>282700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>92500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>52500</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3275,53 +3376,56 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>80600</v>
+      </c>
+      <c r="E47" s="3">
         <v>48800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>35700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>62900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>11000</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>1400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>11100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>20500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>48400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>67700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>65500</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3337,8 +3441,8 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
+      <c r="W47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X47" s="3">
         <v>0</v>
@@ -3349,67 +3453,70 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>40600</v>
+      </c>
+      <c r="E48" s="3">
         <v>41600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>29400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>30600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>31700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>32700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>33600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>34300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>35300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>35500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>34900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>32600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>29000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5100</v>
-      </c>
-      <c r="T48" s="3">
-        <v>5000</v>
       </c>
       <c r="U48" s="3">
         <v>5000</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
+      <c r="V48" s="3">
+        <v>5000</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
@@ -3423,8 +3530,11 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3497,8 +3607,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3684,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,46 +3761,49 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E52" s="3">
         <v>2900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>800</v>
-      </c>
-      <c r="G52" s="3">
-        <v>700</v>
       </c>
       <c r="H52" s="3">
         <v>700</v>
       </c>
       <c r="I52" s="3">
+        <v>700</v>
+      </c>
+      <c r="J52" s="3">
         <v>1100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1300</v>
-      </c>
-      <c r="K52" s="3">
-        <v>1100</v>
       </c>
       <c r="L52" s="3">
         <v>1100</v>
       </c>
       <c r="M52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N52" s="3">
         <v>1000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>900</v>
-      </c>
-      <c r="O52" s="3">
-        <v>600</v>
       </c>
       <c r="P52" s="3">
         <v>600</v>
@@ -3699,13 +3818,13 @@
         <v>600</v>
       </c>
       <c r="T52" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="U52" s="3">
         <v>700</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
+      <c r="V52" s="3">
+        <v>700</v>
       </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
@@ -3719,8 +3838,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,68 +3915,71 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>560400</v>
+      </c>
+      <c r="E54" s="3">
         <v>604000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>620100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>629900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>339900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>361600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>352500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>244000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>261800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>280200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>302900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>324900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>353500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>240600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>254900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>270100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>288300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>98200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>58200</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3867,8 +3992,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4023,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,68 +4052,69 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E57" s="3">
         <v>2900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1700</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3997,22 +4127,25 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E58" s="3">
         <v>5100</v>
-      </c>
-      <c r="E58" s="3">
-        <v>3200</v>
       </c>
       <c r="F58" s="3">
         <v>3200</v>
       </c>
       <c r="G58" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="H58" s="3">
         <v>3100</v>
@@ -4021,11 +4154,11 @@
         <v>3100</v>
       </c>
       <c r="J58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K58" s="3">
         <v>2700</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -4071,68 +4204,71 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
+        <v>300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>0</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3">
         <v>300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>12600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>15000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>13000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>11200</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4145,68 +4281,71 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E60" s="3">
         <v>29500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>19400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>16400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>18200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>13700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>15700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>13600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>14300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>12100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>16300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>11400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>13900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>16700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>14300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>13000</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4219,35 +4358,38 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>19000</v>
+      </c>
+      <c r="E61" s="3">
         <v>19700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>12000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>13000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -4293,8 +4435,11 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4311,50 +4456,50 @@
         <v>600</v>
       </c>
       <c r="H62" s="3">
+        <v>600</v>
+      </c>
+      <c r="I62" s="3">
         <v>400</v>
-      </c>
-      <c r="I62" s="3">
-        <v>200</v>
       </c>
       <c r="J62" s="3">
         <v>200</v>
       </c>
       <c r="K62" s="3">
+        <v>200</v>
+      </c>
+      <c r="L62" s="3">
         <v>14800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>15200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>16100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>18000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>5100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>13800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>15200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>13800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>15300</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4367,8 +4512,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4589,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4666,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,68 +4743,71 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>49800</v>
+      </c>
+      <c r="E66" s="3">
         <v>51100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>31800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>29300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>32100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>31700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>27400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>25400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>30500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>28700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>30400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>28900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>34400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>16500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>14300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>27700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>31900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>28000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>28200</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4663,8 +4820,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4851,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4926,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5003,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4893,14 +5060,14 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
         <v>175400</v>
       </c>
-      <c r="U70" s="3">
+      <c r="V70" s="3">
         <v>103000</v>
       </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
       <c r="W70" s="3">
         <v>0</v>
       </c>
@@ -4913,8 +5080,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,68 +5157,71 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-576200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-526500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-482700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-447700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-415300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-383000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-372800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-343200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-314500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-287100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-261400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-233300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-207000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-181900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-159700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-152100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-135700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-115100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-79000</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5061,8 +5234,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5311,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5388,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,68 +5465,71 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>510600</v>
+      </c>
+      <c r="E76" s="3">
         <v>552900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>588300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>600600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>307800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>329900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>325100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>218600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>231300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>251400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>272500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>296100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>319100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>224100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>240600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>242400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>256400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-105300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-73000</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5357,8 +5542,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5619,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-49700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-43800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-35000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-32400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-32300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-10300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-29600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-28700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-27400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-25700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-28100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-26300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-25100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-22200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-16400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-56700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-36100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-16100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-16700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-16500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-9600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,13 +5809,14 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="E83" s="3">
         <v>1400</v>
@@ -5630,25 +5828,25 @@
         <v>1400</v>
       </c>
       <c r="H83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I83" s="3">
         <v>900</v>
-      </c>
-      <c r="I83" s="3">
-        <v>800</v>
       </c>
       <c r="J83" s="3">
         <v>800</v>
       </c>
       <c r="K83" s="3">
+        <v>800</v>
+      </c>
+      <c r="L83" s="3">
         <v>1000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>500</v>
       </c>
       <c r="M83" s="3">
         <v>500</v>
       </c>
       <c r="N83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="O83" s="3">
         <v>400</v>
@@ -5663,31 +5861,34 @@
         <v>400</v>
       </c>
       <c r="S83" s="3">
+        <v>400</v>
+      </c>
+      <c r="T83" s="3">
         <v>1400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1100</v>
-      </c>
-      <c r="U83" s="3">
-        <v>300</v>
       </c>
       <c r="V83" s="3">
         <v>300</v>
       </c>
       <c r="W83" s="3">
+        <v>300</v>
+      </c>
+      <c r="X83" s="3">
         <v>400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>300</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5961,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6038,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6115,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6192,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,82 +6269,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-45900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-29400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-30200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-29100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-24700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-22100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-27900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-22200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-21000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-19900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-23600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-21800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-15700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-16200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-15400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-50900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-33400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-8700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-10900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-17200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-16300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-6400</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,82 +6377,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1000</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-500</v>
       </c>
       <c r="U91" s="3">
         <v>-500</v>
       </c>
       <c r="V91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="W91" s="3">
         <v>-1100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-400</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6529,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,82 +6606,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E94" s="3">
         <v>27300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-73500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-263300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>30000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>49300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>43100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-35800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>15400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>57500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-54100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-32300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-139000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1000</v>
-      </c>
-      <c r="T94" s="3">
-        <v>-500</v>
       </c>
       <c r="U94" s="3">
         <v>-500</v>
       </c>
       <c r="V94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="W94" s="3">
         <v>-1100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-400</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,8 +6714,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6508,8 +6741,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6556,8 +6789,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6866,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6943,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,8 +7020,11 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6787,73 +7032,76 @@
         <v>600</v>
       </c>
       <c r="E100" s="3">
+        <v>600</v>
+      </c>
+      <c r="F100" s="3">
         <v>17200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>318800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>4800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>10600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>130500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>11000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>116100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>279000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>73000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>84600</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6878,8 +7126,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6926,78 +7174,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-38200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-86500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>26500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-26600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>39400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>157700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>26200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-55900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>37500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-77000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>62000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-152800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-16100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-16900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>227100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>39100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-9800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-13400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-18900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>67900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-6400</v>
       </c>
-      <c r="Z102" s="3" t="s">
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FDMT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FDMT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="92">
   <si>
     <t>FDMT</t>
   </si>
@@ -656,120 +656,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -785,98 +789,101 @@
       <c r="G8" s="3">
         <v>0</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3">
         <v>20200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>14600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>13600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>14600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>14100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5100</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>40700</v>
+      </c>
+      <c r="E9" s="3">
         <v>43100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>38500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>31900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>27900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>26000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>25100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>23600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>22400</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -922,38 +929,41 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-40700</v>
+      </c>
+      <c r="E10" s="3">
         <v>-43100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-38500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-31900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-27800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-26000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-4900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-23300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-22100</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -999,8 +1009,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1028,85 +1041,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>40700</v>
+      </c>
+      <c r="E12" s="3">
         <v>43100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>38500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>31900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>27900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>26000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>25100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>23600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>22400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>21500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>18900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>20400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>19400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>17500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>15800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>15200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>12800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>53000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>40400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>12400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>9400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>17000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>18400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>8200</v>
       </c>
-      <c r="AA12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1182,8 +1199,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1211,8 +1231,8 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1226,8 +1246,8 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
@@ -1235,8 +1255,8 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1245,11 +1265,11 @@
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>5100</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1259,8 +1279,11 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1268,7 +1291,7 @@
         <v>1100</v>
       </c>
       <c r="E15" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="F15" s="3">
         <v>1200</v>
@@ -1277,20 +1300,20 @@
         <v>1200</v>
       </c>
       <c r="H15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I15" s="3">
         <v>1100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1336,8 +1359,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1362,162 +1388,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>53600</v>
+      </c>
+      <c r="E17" s="3">
         <v>56100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>51100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>42500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>38200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>36600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>34200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>32400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>30400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>30000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>27000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>28600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>27600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>24900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>24000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>22200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>18300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>70300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>50800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>18300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>17600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>21900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>24500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>10400</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-53600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-56100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-51100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-42500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-38100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-36700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-14000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-32100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-30100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-28800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-26500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-28400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-26400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-24800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-22600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-7600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-16300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-56700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-36200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-16300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-17100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-17500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-10400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1545,13 +1578,14 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1566,141 +1600,147 @@
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>1400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>400</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-52500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-55000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-49900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-41300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-37000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-35600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-13100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-31000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-29100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-26400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-25200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-27600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-25900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-24700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-21900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-7200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-16000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-55300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-35100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-15800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-16400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-16100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-8900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1728,8 +1768,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1776,85 +1816,91 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-49700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-43800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-35000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-32400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-32300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-10300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-29600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-28700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-27400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-25700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-28100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-26300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-25100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-22200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-7600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-16400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-56700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-36100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-16100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-16700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-16500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-9600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1882,8 +1928,8 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1930,8 +1976,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2007,162 +2056,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-49700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-43800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-35000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-32400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-32300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-10300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-29600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-28700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-27400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-25700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-28100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-26300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-25100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-22200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-7600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-16400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-56700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-36100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-16100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-16700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-16500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-9600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-49700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-43800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-35000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-32400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-32300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-10300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-29600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-28700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-27400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-25700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-28100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-26300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-25100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-22200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-7600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-16400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-56700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-36100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-16100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-16700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-16500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-9600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2238,8 +2296,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2315,8 +2376,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2392,8 +2456,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2469,13 +2536,16 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -2490,141 +2560,147 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-1400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-400</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-49700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-43800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-35000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-32400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-32300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-10300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-29600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-28700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-27400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-25700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-28100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-26300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-25100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-22200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-16400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-56700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-36100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-16100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-16700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-16500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-9600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2700,167 +2776,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-49700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-43800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-35000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-32400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-32300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-10300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-29600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-28700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-27400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-25700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-28100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-26300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-25100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-22200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-16400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-56700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-36100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-16100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-16700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-16500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-9600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2888,8 +2973,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2917,71 +3003,72 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>133500</v>
+      </c>
+      <c r="E41" s="3">
         <v>149300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>187500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>189100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>275600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>249100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>275700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>236300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>78600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>52400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>108300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>113500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>76000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>153000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>91000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>243700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>259900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>276700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>88800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>49700</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2994,56 +3081,59 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>187900</v>
+      </c>
+      <c r="E42" s="3">
         <v>275500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>314400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>352900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>250300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>39100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>44000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>74000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>121900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>161200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>119400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>127600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>160200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>94800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>70700</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3059,8 +3149,8 @@
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
@@ -3071,8 +3161,11 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3100,8 +3193,8 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -3116,26 +3209,26 @@
         <v>0</v>
       </c>
       <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3">
         <v>800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1000</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3148,8 +3241,11 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3177,8 +3273,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3225,8 +3321,11 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3254,42 +3353,42 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>7000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>4800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1900</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3302,71 +3401,74 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>332600</v>
+      </c>
+      <c r="E46" s="3">
         <v>434900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>510800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>552600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>535600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>296600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>328200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>317800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>207000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>220500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>232500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>246500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>243000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>256300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>165700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>248800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>264500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>282700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>92500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>52500</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3379,56 +3481,59 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>137000</v>
+      </c>
+      <c r="E47" s="3">
         <v>80600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>48800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>35700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>62900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>11000</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
         <v>1400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>11100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>20500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>48400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>67700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>65500</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3444,8 +3549,8 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="X47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
@@ -3456,70 +3561,73 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E48" s="3">
         <v>40600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>41600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>29400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>30600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>31700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>32700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>33600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>34300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>35300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>35500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>34900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>32600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>29000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5100</v>
-      </c>
-      <c r="U48" s="3">
-        <v>5000</v>
       </c>
       <c r="V48" s="3">
         <v>5000</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
+      <c r="W48" s="3">
+        <v>5000</v>
       </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
@@ -3533,8 +3641,11 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3610,8 +3721,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3687,8 +3801,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3764,49 +3881,52 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>800</v>
-      </c>
-      <c r="H52" s="3">
-        <v>700</v>
       </c>
       <c r="I52" s="3">
         <v>700</v>
       </c>
       <c r="J52" s="3">
+        <v>700</v>
+      </c>
+      <c r="K52" s="3">
         <v>1100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1300</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1100</v>
       </c>
       <c r="M52" s="3">
         <v>1100</v>
       </c>
       <c r="N52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O52" s="3">
         <v>1000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>900</v>
-      </c>
-      <c r="P52" s="3">
-        <v>600</v>
       </c>
       <c r="Q52" s="3">
         <v>600</v>
@@ -3821,13 +3941,13 @@
         <v>600</v>
       </c>
       <c r="U52" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="V52" s="3">
         <v>700</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
+      <c r="W52" s="3">
+        <v>700</v>
       </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
@@ -3841,8 +3961,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3918,71 +4041,74 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>515700</v>
+      </c>
+      <c r="E54" s="3">
         <v>560400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>604000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>620100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>629900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>339900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>361600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>352500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>244000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>261800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>280200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>302900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>324900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>353500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>240600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>254900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>270100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>288300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>98200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>58200</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3995,8 +4121,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4024,8 +4153,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4053,71 +4183,72 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E57" s="3">
         <v>4400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1700</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4130,25 +4261,28 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E58" s="3">
         <v>5600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5100</v>
-      </c>
-      <c r="F58" s="3">
-        <v>3200</v>
       </c>
       <c r="G58" s="3">
         <v>3200</v>
       </c>
       <c r="H58" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="I58" s="3">
         <v>3100</v>
@@ -4157,11 +4291,11 @@
         <v>3100</v>
       </c>
       <c r="K58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="L58" s="3">
         <v>2700</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4207,71 +4341,74 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>900</v>
+      </c>
+      <c r="E59" s="3">
         <v>300</v>
       </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
+      <c r="F59" s="3">
+        <v>0</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3">
         <v>300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>12600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>15000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>13000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>11200</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4284,71 +4421,74 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E60" s="3">
         <v>29100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>29500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>19400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>16400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>19000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>18200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>13700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>15700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>13600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>14300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>16300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>11400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>13900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>16700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>14300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>13000</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4361,38 +4501,41 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E61" s="3">
         <v>19000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>19700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>11500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>12000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>13000</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -4438,13 +4581,16 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E62" s="3">
         <v>600</v>
@@ -4459,50 +4605,50 @@
         <v>600</v>
       </c>
       <c r="I62" s="3">
+        <v>600</v>
+      </c>
+      <c r="J62" s="3">
         <v>400</v>
-      </c>
-      <c r="J62" s="3">
-        <v>200</v>
       </c>
       <c r="K62" s="3">
         <v>200</v>
       </c>
       <c r="L62" s="3">
+        <v>200</v>
+      </c>
+      <c r="M62" s="3">
         <v>14800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>15200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>18000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>4400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>13800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>15200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>13800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>15300</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4515,8 +4661,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4592,8 +4741,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4669,8 +4821,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4746,71 +4901,74 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E66" s="3">
         <v>49800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>51100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>31800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>29300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>32100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>31700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>27400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>25400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>30500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>28700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>30400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>28900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>34400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>16500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>14300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>27700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>31900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>28000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>28200</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4823,8 +4981,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4852,8 +5013,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4929,8 +5091,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5006,8 +5171,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5063,14 +5231,14 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>175400</v>
       </c>
-      <c r="V70" s="3">
+      <c r="W70" s="3">
         <v>103000</v>
       </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
@@ -5083,8 +5251,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5160,71 +5331,74 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-624200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-576200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-526500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-482700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-447700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-415300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-383000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-372800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-343200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-314500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-287100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-261400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-233300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-207000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-181900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-159700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-152100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-135700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-115100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-79000</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5237,8 +5411,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5314,8 +5491,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5391,8 +5571,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5468,71 +5651,74 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>469700</v>
+      </c>
+      <c r="E76" s="3">
         <v>510600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>552900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>588300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>600600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>307800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>329900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>325100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>218600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>231300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>251400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>272500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>296100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>319100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>224100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>240600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>242400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>256400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-105300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-73000</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5545,8 +5731,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5622,167 +5811,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-48000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-49700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-43800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-35000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-32400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-32300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-10300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-29600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-28700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-27400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-25700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-28100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-26300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-25100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-22200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-16400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-56700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-36100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-16100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-16700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-16500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-9600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5810,16 +6008,17 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E83" s="3">
         <v>1500</v>
-      </c>
-      <c r="E83" s="3">
-        <v>1400</v>
       </c>
       <c r="F83" s="3">
         <v>1400</v>
@@ -5831,25 +6030,25 @@
         <v>1400</v>
       </c>
       <c r="I83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J83" s="3">
         <v>900</v>
-      </c>
-      <c r="J83" s="3">
-        <v>800</v>
       </c>
       <c r="K83" s="3">
         <v>800</v>
       </c>
       <c r="L83" s="3">
+        <v>800</v>
+      </c>
+      <c r="M83" s="3">
         <v>1000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>500</v>
       </c>
       <c r="N83" s="3">
         <v>500</v>
       </c>
       <c r="O83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="P83" s="3">
         <v>400</v>
@@ -5864,31 +6063,34 @@
         <v>400</v>
       </c>
       <c r="T83" s="3">
+        <v>400</v>
+      </c>
+      <c r="U83" s="3">
         <v>1400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1100</v>
-      </c>
-      <c r="V83" s="3">
-        <v>300</v>
       </c>
       <c r="W83" s="3">
         <v>300</v>
       </c>
       <c r="X83" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y83" s="3">
         <v>400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>300</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5964,8 +6166,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6041,8 +6246,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6118,8 +6326,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6195,8 +6406,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6272,85 +6486,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-47800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-45900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-29400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-30200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-29100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-24700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-22100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-27900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-22200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-21000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-19900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-23600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-21800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-15700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-16200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-15400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-50900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-33400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-8700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-10900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-17200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-16300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-6400</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6378,85 +6598,89 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1000</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-500</v>
       </c>
       <c r="V91" s="3">
         <v>-500</v>
       </c>
       <c r="W91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="X91" s="3">
         <v>-1100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-400</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6532,8 +6756,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6609,85 +6836,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>31900</v>
+      </c>
+      <c r="E94" s="3">
         <v>7100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>27300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-73500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-263300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>30000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>49300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>43100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-35800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>15400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>57500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-54100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-32300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-139000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1000</v>
-      </c>
-      <c r="U94" s="3">
-        <v>-500</v>
       </c>
       <c r="V94" s="3">
         <v>-500</v>
       </c>
       <c r="W94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="X94" s="3">
         <v>-1100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-400</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6715,8 +6948,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6744,8 +6978,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6792,8 +7026,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6869,8 +7106,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6946,8 +7186,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7023,85 +7266,91 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>600</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E100" s="3">
         <v>600</v>
       </c>
       <c r="F100" s="3">
+        <v>600</v>
+      </c>
+      <c r="G100" s="3">
         <v>17200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>318800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>4800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>10600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>130500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>11000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>116100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>279000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>73000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>84600</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7129,8 +7378,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7177,81 +7426,87 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-38200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-86500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>26500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-26600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>39400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>157700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>26200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-55900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>37500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-77000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>62000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-152800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-16100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-16900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>227100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>39100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-9800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-13400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-18900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>67900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-6400</v>
       </c>
-      <c r="AA102" s="3" t="s">
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FDMT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FDMT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
   <si>
     <t>FDMT</t>
   </si>
@@ -656,124 +656,128 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -792,101 +796,104 @@
       <c r="H8" s="3">
         <v>0</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3">
         <v>20200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>14600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>13600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>14600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>14100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5100</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E9" s="3">
         <v>40700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>43100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>38500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>31900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>27900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>26000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>25100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>23600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>22400</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -932,41 +939,44 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-47900</v>
+      </c>
+      <c r="E10" s="3">
         <v>-40700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-43100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-38500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-31900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-27800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-26000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-4900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-23300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-22100</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1012,8 +1022,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1042,88 +1055,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E12" s="3">
         <v>40700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>43100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>38500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>31900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>27900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>26000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>25100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>23600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>22400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>21500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>18900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>20400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>19400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>17500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>15800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>15200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>12800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>53000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>40400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>12400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>9400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>17000</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>18400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>8200</v>
       </c>
-      <c r="AB12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1202,8 +1219,11 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1234,8 +1254,8 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1249,8 +1269,8 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
@@ -1258,8 +1278,8 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1268,11 +1288,11 @@
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>5100</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1282,19 +1302,22 @@
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="E15" s="3">
         <v>1100</v>
       </c>
       <c r="F15" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="G15" s="3">
         <v>1200</v>
@@ -1303,20 +1326,20 @@
         <v>1200</v>
       </c>
       <c r="I15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J15" s="3">
         <v>1100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1000</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1362,8 +1385,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1389,168 +1415,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>59500</v>
+      </c>
+      <c r="E17" s="3">
         <v>53600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>56100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>51100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>42500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>38200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>36600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>34200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>32400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>30400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>30000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>27000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>28600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>27600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>24900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>24000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>22200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>18300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>70300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>50800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>18300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>17600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>21900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>24500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>10400</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-59500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-53600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-56100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-51100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-42500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-38100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-36700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-14000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-32100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-30100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-28800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-26500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-28400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-26400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-24800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-22600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-7600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-16300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-56700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-36200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-16300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-17100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-17500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-10400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-5300</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1579,17 +1612,18 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
@@ -1603,144 +1637,150 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>1400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>400</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-58400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-52500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-55000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-49900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-41300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-37000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-35600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-13100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-31000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-29100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-26400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-25200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-27600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-25900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-24700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-21900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-7200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-16000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-55300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-35100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-15800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-16400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-16100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-8900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1771,8 +1811,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1819,88 +1859,94 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-54700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-48000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-49700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-43800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-35000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-32400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-32300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-10300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-29600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-28700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-27400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-25700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-28100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-26300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-25100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-22200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-7600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-16400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-56700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-36100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-16100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-16700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-16500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-9600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1931,8 +1977,8 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
@@ -1979,8 +2025,11 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2059,168 +2108,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-54700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-48000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-49700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-43800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-35000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-32400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-32300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-10300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-29600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-28700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-27400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-25700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-28100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-26300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-25100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-22200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-7600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-16400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-56700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-36100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-16100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-16700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-16500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-9600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-54700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-48000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-49700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-43800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-35000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-32400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-32300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-10300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-29600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-28700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-27400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-25700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-28100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-26300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-25100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-22200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-7600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-16400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-56700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-36100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-16100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-16700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-16500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-9600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2299,8 +2357,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2379,8 +2440,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2459,8 +2523,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2539,17 +2606,20 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
@@ -2563,144 +2633,150 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-1400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-400</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-54700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-48000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-49700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-43800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-35000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-32400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-32300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-10300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-29600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-28700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-27400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-25700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-28100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-26300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-25100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-22200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-7600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-16400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-56700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-36100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-16100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-16700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-16500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-9600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2779,173 +2855,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-54700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-48000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-49700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-43800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-35000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-32400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-32300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-10300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-29600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-28700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-27400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-25700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-28100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-26300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-25100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-22200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-7600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-16400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-56700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-36100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-16100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-16700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-16500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-9600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2974,8 +3059,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3004,74 +3090,75 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>77200</v>
+      </c>
+      <c r="E41" s="3">
         <v>133500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>149300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>187500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>189100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>275600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>249100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>275700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>236300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>78600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>52400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>108300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>113500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>76000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>153000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>91000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>243700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>259900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>276700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>88800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>49700</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3084,59 +3171,62 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>216100</v>
+      </c>
+      <c r="E42" s="3">
         <v>187900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>275500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>314400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>352900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>250300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>39100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>44000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>74000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>121900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>161200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>119400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>127600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>160200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>94800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>70700</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3152,8 +3242,8 @@
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
@@ -3164,8 +3254,11 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3196,8 +3289,8 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N43" s="3">
         <v>0</v>
@@ -3212,26 +3305,26 @@
         <v>0</v>
       </c>
       <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
         <v>800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1000</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3244,8 +3337,11 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3276,8 +3372,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3324,8 +3420,11 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3356,42 +3455,42 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>7000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>8500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>3700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1900</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3404,74 +3503,77 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>303300</v>
+      </c>
+      <c r="E46" s="3">
         <v>332600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>434900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>510800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>552600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>535600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>296600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>328200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>317800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>207000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>220500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>232500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>246500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>243000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>256300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>165700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>248800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>264500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>282700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>92500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>52500</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3484,59 +3586,62 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>123800</v>
+      </c>
+      <c r="E47" s="3">
         <v>137000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>80600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>48800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>35700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>62900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>11000</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
         <v>1400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>11100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>20500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>48400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>67700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>65500</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3552,8 +3657,8 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
@@ -3564,73 +3669,76 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>37200</v>
+      </c>
+      <c r="E48" s="3">
         <v>39100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>40600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>41600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>29400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>30600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>31700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>32700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>33600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>34300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>35300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>35500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>34900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>32600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>29000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5100</v>
-      </c>
-      <c r="V48" s="3">
-        <v>5000</v>
       </c>
       <c r="W48" s="3">
         <v>5000</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
+      <c r="X48" s="3">
+        <v>5000</v>
       </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
@@ -3644,8 +3752,11 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3724,8 +3835,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3804,8 +3918,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3884,52 +4001,55 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E52" s="3">
         <v>7000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>800</v>
-      </c>
-      <c r="I52" s="3">
-        <v>700</v>
       </c>
       <c r="J52" s="3">
         <v>700</v>
       </c>
       <c r="K52" s="3">
+        <v>700</v>
+      </c>
+      <c r="L52" s="3">
         <v>1100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1300</v>
-      </c>
-      <c r="M52" s="3">
-        <v>1100</v>
       </c>
       <c r="N52" s="3">
         <v>1100</v>
       </c>
       <c r="O52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P52" s="3">
         <v>1000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>900</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>600</v>
       </c>
       <c r="R52" s="3">
         <v>600</v>
@@ -3944,13 +4064,13 @@
         <v>600</v>
       </c>
       <c r="V52" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="W52" s="3">
         <v>700</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
+      <c r="X52" s="3">
+        <v>700</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
@@ -3964,8 +4084,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4044,74 +4167,77 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>473600</v>
+      </c>
+      <c r="E54" s="3">
         <v>515700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>560400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>604000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>620100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>629900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>339900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>361600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>352500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>244000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>261800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>280200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>302900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>324900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>353500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>240600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>254900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>270100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>288300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>98200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>58200</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4124,8 +4250,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4154,8 +4283,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4184,74 +4314,75 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E57" s="3">
         <v>4200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1700</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4264,8 +4395,11 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4273,19 +4407,19 @@
         <v>5700</v>
       </c>
       <c r="E58" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F58" s="3">
         <v>5600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5100</v>
-      </c>
-      <c r="G58" s="3">
-        <v>3200</v>
       </c>
       <c r="H58" s="3">
         <v>3200</v>
       </c>
       <c r="I58" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="J58" s="3">
         <v>3100</v>
@@ -4294,11 +4428,11 @@
         <v>3100</v>
       </c>
       <c r="L58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="M58" s="3">
         <v>2700</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -4344,74 +4478,77 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E59" s="3">
         <v>900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>300</v>
       </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
+      <c r="G59" s="3">
+        <v>0</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3">
         <v>300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>12400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>12600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>15000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>13000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>11200</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4424,74 +4561,77 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>34700</v>
+      </c>
+      <c r="E60" s="3">
         <v>26900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>29100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>29500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>16400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>19000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>18200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>13700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>15700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>13600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>16300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>11400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>9900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>13900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>16700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>14300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>13000</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4504,41 +4644,44 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E61" s="3">
         <v>18200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>19000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>19700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>10500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>11000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>12500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>13000</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -4584,8 +4727,11 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4593,7 +4739,7 @@
         <v>500</v>
       </c>
       <c r="E62" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="F62" s="3">
         <v>600</v>
@@ -4608,50 +4754,50 @@
         <v>600</v>
       </c>
       <c r="J62" s="3">
+        <v>600</v>
+      </c>
+      <c r="K62" s="3">
         <v>400</v>
-      </c>
-      <c r="K62" s="3">
-        <v>200</v>
       </c>
       <c r="L62" s="3">
         <v>200</v>
       </c>
       <c r="M62" s="3">
+        <v>200</v>
+      </c>
+      <c r="N62" s="3">
         <v>14800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>15200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>16800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>18000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>13800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>15200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>13800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>15300</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4664,8 +4810,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4744,8 +4893,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4824,8 +4976,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4904,74 +5059,77 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>52700</v>
+      </c>
+      <c r="E66" s="3">
         <v>46000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>49800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>51100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>31800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>29300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>32100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>31700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>27400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>25400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>30500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>28700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>30400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>28900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>34400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>16500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>14300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>27700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>31900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>28000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>28200</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4984,8 +5142,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5014,8 +5175,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5094,8 +5256,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5174,8 +5339,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5234,14 +5402,14 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>175400</v>
       </c>
-      <c r="W70" s="3">
+      <c r="X70" s="3">
         <v>103000</v>
       </c>
-      <c r="X70" s="3">
-        <v>0</v>
-      </c>
       <c r="Y70" s="3">
         <v>0</v>
       </c>
@@ -5254,8 +5422,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5334,74 +5505,77 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-678800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-624200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-576200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-526500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-482700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-447700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-415300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-383000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-372800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-343200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-314500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-287100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-261400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-233300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-207000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-181900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-159700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-152100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-135700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-115100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-79000</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5414,8 +5588,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5494,8 +5671,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5574,8 +5754,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5654,74 +5837,77 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>420900</v>
+      </c>
+      <c r="E76" s="3">
         <v>469700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>510600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>552900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>588300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>600600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>307800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>329900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>325100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>218600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>231300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>251400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>272500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>296100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>319100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>224100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>240600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>242400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>256400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-105300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-73000</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5734,8 +5920,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5814,173 +6003,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-54700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-48000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-49700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-43800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-35000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-32400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-32300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-10300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-29600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-28700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-27400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-25700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-28100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-26300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-25100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-22200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-7600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-16400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-56700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-36100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-16100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-16700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-16500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-9600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6009,8 +6207,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6018,10 +6217,10 @@
         <v>1600</v>
       </c>
       <c r="E83" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F83" s="3">
         <v>1500</v>
-      </c>
-      <c r="F83" s="3">
-        <v>1400</v>
       </c>
       <c r="G83" s="3">
         <v>1400</v>
@@ -6033,25 +6232,25 @@
         <v>1400</v>
       </c>
       <c r="J83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K83" s="3">
         <v>900</v>
-      </c>
-      <c r="K83" s="3">
-        <v>800</v>
       </c>
       <c r="L83" s="3">
         <v>800</v>
       </c>
       <c r="M83" s="3">
+        <v>800</v>
+      </c>
+      <c r="N83" s="3">
         <v>1000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>500</v>
       </c>
       <c r="O83" s="3">
         <v>500</v>
       </c>
       <c r="P83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="Q83" s="3">
         <v>400</v>
@@ -6066,31 +6265,34 @@
         <v>400</v>
       </c>
       <c r="U83" s="3">
+        <v>400</v>
+      </c>
+      <c r="V83" s="3">
         <v>1400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1100</v>
-      </c>
-      <c r="W83" s="3">
-        <v>300</v>
       </c>
       <c r="X83" s="3">
         <v>300</v>
       </c>
       <c r="Y83" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z83" s="3">
         <v>400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>300</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6169,8 +6371,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6249,8 +6454,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6329,8 +6537,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6409,8 +6620,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6489,88 +6703,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-43400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-47800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-45900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-29400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-30200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-29100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-24700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-22100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-27900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-22200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-21000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-19900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-23600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-21800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-15700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-16200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-15400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-50900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-33400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-8700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-10900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-17200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-16300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-6400</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6599,88 +6819,92 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1000</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-500</v>
       </c>
       <c r="W91" s="3">
         <v>-500</v>
       </c>
       <c r="X91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-400</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6759,8 +6983,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6839,88 +7066,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="E94" s="3">
         <v>31900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>7100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>27300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-73500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-263300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>30000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>49300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>43100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-35800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>15400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>57500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-54100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-32300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-139000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1000</v>
-      </c>
-      <c r="V94" s="3">
-        <v>-500</v>
       </c>
       <c r="W94" s="3">
         <v>-500</v>
       </c>
       <c r="X94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-400</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6949,8 +7182,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6981,8 +7215,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7029,8 +7263,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7109,8 +7346,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7189,8 +7429,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7269,88 +7512,94 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E100" s="3">
-        <v>600</v>
+      <c r="D100" s="3">
+        <v>900</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F100" s="3">
         <v>600</v>
       </c>
       <c r="G100" s="3">
+        <v>600</v>
+      </c>
+      <c r="H100" s="3">
         <v>17200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>318800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>4800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>10600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>130500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>11000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>116100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>279000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>73000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>84600</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7381,8 +7630,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -7429,84 +7678,90 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-56400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-15800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-38200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-86500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>26500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-26600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>39400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>157700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>26200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-55900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>37500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-77000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>62000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-152800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-16100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-16900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>227100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>39100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-9800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-13400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-18900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>67900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-6400</v>
       </c>
-      <c r="AB102" s="3" t="s">
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FDMT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FDMT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
   <si>
     <t>FDMT</t>
   </si>
@@ -656,143 +656,150 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>3000</v>
       </c>
       <c r="E8" s="3">
-        <v>0</v>
+        <v>85100</v>
       </c>
       <c r="F8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -806,110 +813,116 @@
       <c r="J8" s="3">
         <v>0</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
+      <c r="K8" s="3">
+        <v>0</v>
       </c>
       <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3">
         <v>20200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>14600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>2000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>13600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>14600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>2000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>4400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>14100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>5100</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>65000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>57500</v>
+      </c>
+      <c r="F9" s="3">
         <v>47200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>48000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>40700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>43100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>38500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>31900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>27900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>26000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>25100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>23600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>22400</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -952,50 +965,56 @@
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-61900</v>
+      </c>
+      <c r="E10" s="3">
+        <v>27600</v>
+      </c>
+      <c r="F10" s="3">
         <v>-47100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>-47900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>-40700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>-43100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>-38500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-31900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>-27800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>-26000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>-4900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>-23300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>-22100</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1038,8 +1057,14 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1070,94 +1095,102 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>65000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>57600</v>
+      </c>
+      <c r="F12" s="3">
         <v>49400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>48000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>40700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>43100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>38500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>31900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>27900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>26000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>25100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>23600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>22400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>21500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>18900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>20400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>19400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>17500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>15800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>15200</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>12800</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>53000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>40400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>12400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>9400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>17000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>18400</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>8200</v>
       </c>
-      <c r="AD12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1242,20 +1275,26 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
+        <v>100</v>
+      </c>
+      <c r="F14" s="3">
         <v>2200</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1280,11 +1319,11 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1295,41 +1334,47 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>5100</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1340,25 +1385,25 @@
         <v>1200</v>
       </c>
       <c r="F15" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H15" s="3">
         <v>1100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>1100</v>
-      </c>
-      <c r="H15" s="3">
-        <v>1200</v>
-      </c>
-      <c r="I15" s="3">
-        <v>1200</v>
       </c>
       <c r="J15" s="3">
         <v>1200</v>
       </c>
       <c r="K15" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="L15" s="3">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="M15" s="3">
         <v>1100</v>
@@ -1367,10 +1412,10 @@
         <v>1000</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1414,8 +1459,14 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1443,180 +1494,194 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>76700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>70300</v>
+      </c>
+      <c r="F17" s="3">
         <v>59100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>59500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>53600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>56100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>51100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>42500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>38200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>36600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>34200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>32400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>30400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>30000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>27000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>28600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>27600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>24900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>24000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>22200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>18300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>70300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>50800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>18300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>17600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>21900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>24500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>10400</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-73600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>14800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-59000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-59500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-53600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-56100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-51100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-42500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-38100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-36700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-14000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-32100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-30100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-28800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-26500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-28400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-26400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-24800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-22600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-7600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-16300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-56700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-36200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-16300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-17100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-17500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-10400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-5300</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1647,8 +1712,10 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1656,17 +1723,17 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
@@ -1677,150 +1744,162 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>1400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>400</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>1000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>100</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-72400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>16000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-57700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-58400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-52500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-55000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-49900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-41300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-37000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-35600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-13100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-31000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-29100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-26400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-25200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-27600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-25900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-24700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-21900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-7200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-16000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-55300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-35100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-15800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-16400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-16100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-8900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1857,11 +1936,11 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1905,94 +1984,106 @@
       <c r="AD22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-68800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>19400</v>
+      </c>
+      <c r="F23" s="3">
         <v>-56900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-54700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-48000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-49700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-43800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-35000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-32400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-32300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-10300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-29600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-28700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-27400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-25700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-28100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-26300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-25100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-22200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-7600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-16400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-56700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-36100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-16100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-16700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-16500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-9600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2029,11 +2120,11 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -2077,8 +2168,14 @@
       <c r="AD24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2163,180 +2260,198 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-68800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>19400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-56900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-54700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-48000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-49700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-43800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-35000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-32400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-32300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-10300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-29600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-28700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-27400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-25700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-28100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-26300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-25100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-22200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-7600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-16400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-56700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-36100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-16100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-16700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-16500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-9600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-68800</v>
+      </c>
+      <c r="E27" s="3">
+        <v>19400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-56900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-54700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-48000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-49700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-43800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-35000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-32400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-32300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-10300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-29600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-28700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-27400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-25700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-28100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-26300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-25100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-22200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-7600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-16400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-56700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-36100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-16100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-16700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-16500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-9600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2421,8 +2536,14 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2507,8 +2628,14 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2593,8 +2720,14 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2679,8 +2812,14 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2688,17 +2827,17 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
@@ -2709,150 +2848,162 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-1400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-400</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-100</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-68800</v>
+      </c>
+      <c r="E33" s="3">
+        <v>19400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-56900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-54700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-48000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-49700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-43800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-35000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-32400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-32300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-10300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-29600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-28700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-27400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-25700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-28100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-26300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-25100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-22200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-7600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-16400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-56700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-36100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-16100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-16700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-16500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-9600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2937,185 +3088,203 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-68800</v>
+      </c>
+      <c r="E35" s="3">
+        <v>19400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-56900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-54700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-48000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-49700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-43800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-35000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-32400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-32300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-10300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-29600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-28700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-27400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-25700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-28100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-26300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-25100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-22200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-7600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-16400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-56700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-36100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-16100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-16700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-16500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-9600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3146,8 +3315,10 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3178,83 +3349,85 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>72500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>60200</v>
+      </c>
+      <c r="F41" s="3">
         <v>48600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>77200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>133500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>149300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>187500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>189100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>275600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>249100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>275700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>236300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>78600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>52400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>108300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>113500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>76000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>153000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>91000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>243700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>259900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>276700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>88800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>49700</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3264,68 +3437,74 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>318400</v>
+      </c>
+      <c r="E42" s="3">
+        <v>342400</v>
+      </c>
+      <c r="F42" s="3">
         <v>256500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>216100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>187900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>275500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>314400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>352900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>250300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>39100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>44000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>74000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>121900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>161200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>119400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>127600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>160200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>94800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>70700</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3338,11 +3517,11 @@
       <c r="Z42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB42" s="3">
-        <v>0</v>
+      <c r="AA42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC42" s="3">
         <v>0</v>
@@ -3350,8 +3529,14 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3388,11 +3573,11 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -3404,29 +3589,29 @@
         <v>0</v>
       </c>
       <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3">
         <v>800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>1500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>1000</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3436,8 +3621,14 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3474,11 +3665,11 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3522,8 +3713,14 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3560,45 +3757,45 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>7000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>4800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>5400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>6900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>8500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>3300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>3800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>3700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>4400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>2900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>1900</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3608,83 +3805,89 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>405400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>413100</v>
+      </c>
+      <c r="F46" s="3">
         <v>312400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>303300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>332600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>434900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>510800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>552600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>535600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>296600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>328200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>317800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>207000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>220500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>232500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>246500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>243000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>256300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>165700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>248800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>264500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>282700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>92500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>52500</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3694,68 +3897,74 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>66700</v>
+      </c>
+      <c r="E47" s="3">
+        <v>111400</v>
+      </c>
+      <c r="F47" s="3">
         <v>67200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>123800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>137000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>80600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>48800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>35700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>62900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>11000</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3">
         <v>1400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>4900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>11100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>20500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>48400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>67700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>65500</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3768,11 +3977,11 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB47" s="3">
-        <v>0</v>
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC47" s="3">
         <v>0</v>
@@ -3780,82 +3989,88 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E48" s="3">
+        <v>33000</v>
+      </c>
+      <c r="F48" s="3">
         <v>35100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>37200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>39100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>40600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>41600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>29400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>30600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>31700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>32700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>33600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>34300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>35300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>35500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>34900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>32600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>29000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>8800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>5600</v>
-      </c>
-      <c r="V48" s="3">
-        <v>5000</v>
-      </c>
-      <c r="W48" s="3">
-        <v>5100</v>
       </c>
       <c r="X48" s="3">
         <v>5000</v>
       </c>
       <c r="Y48" s="3">
+        <v>5100</v>
+      </c>
+      <c r="Z48" s="3">
         <v>5000</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA48" s="3" t="s">
-        <v>3</v>
+      <c r="AA48" s="3">
+        <v>5000</v>
       </c>
       <c r="AB48" s="3" t="s">
         <v>3</v>
@@ -3866,8 +4081,14 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3952,8 +4173,14 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4038,8 +4265,14 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4124,61 +4357,67 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>9200</v>
+      </c>
+      <c r="F52" s="3">
         <v>9400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>9400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>7000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>4300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>2900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>2300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>700</v>
-      </c>
-      <c r="M52" s="3">
-        <v>1100</v>
-      </c>
-      <c r="N52" s="3">
-        <v>1300</v>
       </c>
       <c r="O52" s="3">
         <v>1100</v>
       </c>
       <c r="P52" s="3">
+        <v>1300</v>
+      </c>
+      <c r="Q52" s="3">
         <v>1100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="S52" s="3">
         <v>1000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>900</v>
-      </c>
-      <c r="S52" s="3">
-        <v>600</v>
-      </c>
-      <c r="T52" s="3">
-        <v>600</v>
       </c>
       <c r="U52" s="3">
         <v>600</v>
@@ -4190,17 +4429,17 @@
         <v>600</v>
       </c>
       <c r="X52" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z52" s="3">
         <v>700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>700</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4210,8 +4449,14 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4296,83 +4541,89 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>512900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>566700</v>
+      </c>
+      <c r="F54" s="3">
         <v>424000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>473600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>515700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>560400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>604000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>620100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>629900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>339900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>361600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>352500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>244000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>261800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>280200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>302900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>324900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>353500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>240600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>254900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>270100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>288300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>98200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>58200</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4382,8 +4633,14 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4414,8 +4671,10 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4446,83 +4705,85 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>11200</v>
+      </c>
+      <c r="F57" s="3">
         <v>6900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>8700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>4200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>4400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>3400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>4200</v>
-      </c>
-      <c r="K57" s="3">
-        <v>3500</v>
-      </c>
-      <c r="L57" s="3">
-        <v>4700</v>
       </c>
       <c r="M57" s="3">
         <v>3500</v>
       </c>
       <c r="N57" s="3">
+        <v>4700</v>
+      </c>
+      <c r="O57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="P57" s="3">
         <v>2400</v>
-      </c>
-      <c r="O57" s="3">
-        <v>3300</v>
-      </c>
-      <c r="P57" s="3">
-        <v>1500</v>
       </c>
       <c r="Q57" s="3">
         <v>3300</v>
       </c>
       <c r="R57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="S57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="T57" s="3">
         <v>2700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>4800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>3700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>2000</v>
-      </c>
-      <c r="V57" s="3">
-        <v>1300</v>
-      </c>
-      <c r="W57" s="3">
-        <v>1800</v>
       </c>
       <c r="X57" s="3">
         <v>1300</v>
       </c>
       <c r="Y57" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Z57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AA57" s="3">
         <v>1700</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4532,50 +4793,56 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5700</v>
+        <v>5500</v>
       </c>
       <c r="E58" s="3">
-        <v>5700</v>
+        <v>5600</v>
       </c>
       <c r="F58" s="3">
         <v>5700</v>
       </c>
       <c r="G58" s="3">
+        <v>5700</v>
+      </c>
+      <c r="H58" s="3">
+        <v>5700</v>
+      </c>
+      <c r="I58" s="3">
         <v>5600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>5100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>3200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>3200</v>
-      </c>
-      <c r="K58" s="3">
-        <v>3100</v>
-      </c>
-      <c r="L58" s="3">
-        <v>3100</v>
       </c>
       <c r="M58" s="3">
         <v>3100</v>
       </c>
       <c r="N58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="O58" s="3">
+        <v>3100</v>
+      </c>
+      <c r="P58" s="3">
         <v>2700</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -4618,8 +4885,14 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4627,74 +4900,74 @@
         <v>400</v>
       </c>
       <c r="E59" s="3">
+        <v>400</v>
+      </c>
+      <c r="F59" s="3">
+        <v>400</v>
+      </c>
+      <c r="G59" s="3">
         <v>1100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>300</v>
       </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="J59" s="3">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>12400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>12100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>11000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>9400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>11600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>7700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>7900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>12600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>15000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>13000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>11200</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4704,83 +4977,89 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>43400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>44000</v>
+      </c>
+      <c r="F60" s="3">
         <v>37100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>34700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>26900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>29100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>29500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>19400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>16400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>19000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>18200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>13700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>11300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>15700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>13600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>14300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>12100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>16300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>11400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>9900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>13900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>16700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>14300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>13000</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,50 +5069,56 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>15800</v>
+      </c>
+      <c r="F61" s="3">
         <v>16600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>17400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>18200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>19000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>19700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>10500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>11000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>11500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>12000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>12500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>13000</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -4876,8 +5161,14 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4891,10 +5182,10 @@
         <v>500</v>
       </c>
       <c r="G62" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="H62" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I62" s="3">
         <v>600</v>
@@ -4906,53 +5197,53 @@
         <v>600</v>
       </c>
       <c r="L62" s="3">
+        <v>600</v>
+      </c>
+      <c r="M62" s="3">
+        <v>600</v>
+      </c>
+      <c r="N62" s="3">
         <v>400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>14800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>15200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>16100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>16800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>18000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>5100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>4400</v>
-      </c>
-      <c r="V62" s="3">
-        <v>13800</v>
-      </c>
-      <c r="W62" s="3">
-        <v>15200</v>
       </c>
       <c r="X62" s="3">
         <v>13800</v>
       </c>
       <c r="Y62" s="3">
+        <v>15200</v>
+      </c>
+      <c r="Z62" s="3">
+        <v>13800</v>
+      </c>
+      <c r="AA62" s="3">
         <v>15300</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4962,8 +5253,14 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5048,8 +5345,14 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5134,8 +5437,14 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5220,83 +5529,89 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>61100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>61000</v>
+      </c>
+      <c r="F66" s="3">
         <v>55000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>52700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>46000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>49800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>51100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>31800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>29300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>32100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>31700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>27400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>25400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>30500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>28700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>30400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>28900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>34400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>16500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>14300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>27700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>31900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>28000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>28200</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5306,8 +5621,14 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5338,8 +5659,10 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5424,8 +5747,14 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5510,8 +5839,14 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5576,17 +5911,17 @@
         <v>0</v>
       </c>
       <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="3">
         <v>175400</v>
       </c>
-      <c r="Y70" s="3">
+      <c r="AA70" s="3">
         <v>103000</v>
       </c>
-      <c r="Z70" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA70" s="3">
-        <v>0</v>
-      </c>
       <c r="AB70" s="3">
         <v>0</v>
       </c>
@@ -5596,8 +5931,14 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5682,83 +6023,89 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-785100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-716300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-735700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-678800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-624200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-576200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-526500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-482700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-447700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-415300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-383000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-372800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-343200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-314500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-287100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-261400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-233300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-207000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-181900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-159700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-152100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-135700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-115100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-79000</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5768,8 +6115,14 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5854,8 +6207,14 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5940,8 +6299,14 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6026,83 +6391,89 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>451800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>505700</v>
+      </c>
+      <c r="F76" s="3">
         <v>369000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>420900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>469700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>510600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>552900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>588300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>600600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>307800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>329900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>325100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>218600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>231300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>251400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>272500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>296100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>319100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>224100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>240600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>242400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>256400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>-105300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>-73000</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6112,8 +6483,14 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6198,185 +6575,203 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-68800</v>
+      </c>
+      <c r="E81" s="3">
+        <v>19400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-56900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-54700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-48000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-49700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-43800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-35000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-32400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-32300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-10300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-29600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-28700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-27400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-25700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-28100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-26300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-25100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-22200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-7600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-16400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-56700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-36100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-16100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-16700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-16500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-9600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6407,28 +6802,30 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F83" s="3">
         <v>1700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>1600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>1500</v>
-      </c>
-      <c r="H83" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I83" s="3">
-        <v>1400</v>
       </c>
       <c r="J83" s="3">
         <v>1400</v>
@@ -6437,28 +6834,28 @@
         <v>1400</v>
       </c>
       <c r="L83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N83" s="3">
         <v>900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>1000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>500</v>
-      </c>
-      <c r="R83" s="3">
-        <v>400</v>
-      </c>
-      <c r="S83" s="3">
-        <v>400</v>
       </c>
       <c r="T83" s="3">
         <v>400</v>
@@ -6470,31 +6867,37 @@
         <v>400</v>
       </c>
       <c r="W83" s="3">
+        <v>400</v>
+      </c>
+      <c r="X83" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y83" s="3">
         <v>1400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>1100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>300</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6579,8 +6982,14 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6665,8 +7074,14 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6751,8 +7166,14 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6837,8 +7258,14 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6923,94 +7350,106 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-68100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>28600</v>
+      </c>
+      <c r="F89" s="3">
         <v>-46500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-43400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-47800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-45900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-29400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-30200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-29100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-24700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-1200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-22100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-27900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-22200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-19900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-23600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-21800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-15700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-16200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-15400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-50900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-33400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-8700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-10900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-17200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-16300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-6400</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7041,94 +7480,102 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3">
         <v>100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
+        <v>100</v>
+      </c>
+      <c r="G91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-1800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-1000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-1100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-2100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-6400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-5100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-2600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-1000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-400</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7213,8 +7660,14 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7299,94 +7752,106 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>68900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-128800</v>
+      </c>
+      <c r="F94" s="3">
         <v>17800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-13900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>31900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>7100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>27300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-73500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-263300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-6700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>30000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>49300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>43100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-35800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>15400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>57500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-54100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-32300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-139000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-1000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-400</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7417,8 +7882,10 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7455,11 +7922,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7503,8 +7970,14 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7589,8 +8062,14 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7675,8 +8154,14 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7761,94 +8246,106 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>112000</v>
+      </c>
+      <c r="F100" s="3">
         <v>100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>900</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3">
         <v>600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>17200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>318800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>4800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>10600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>130500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>11000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>2000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>116100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>2000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>279000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>73000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>84600</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7885,11 +8382,11 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -7933,90 +8430,102 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>11700</v>
+      </c>
+      <c r="F102" s="3">
         <v>-28600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-56400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-15800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-38200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-1500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-86500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>26500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-26600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>39400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>157700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>26200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-55900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>37500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-77000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>62000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-152800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-16100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-16900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>227100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>39100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-9800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-13400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-18900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>67900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-6400</v>
       </c>
-      <c r="AD102" s="3" t="s">
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
